--- a/2432S028.xlsx
+++ b/2432S028.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kunikata\Desktop\xptouch\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kunikata\Desktop\xptouch_base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34531131-253E-4EAF-A036-664B977036B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D0B12F-DEA8-4FC0-8B0C-5478CE02A2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{3B433E45-3806-4035-B9E5-3F86EFD58587}"/>
+    <workbookView xWindow="31220" yWindow="2780" windowWidth="32780" windowHeight="18080" xr2:uid="{3B433E45-3806-4035-B9E5-3F86EFD58587}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="316">
   <si>
     <t>Onboard Equipment</t>
   </si>
@@ -2358,6 +2358,61 @@
   </si>
   <si>
     <t>Sunton_2432S028 TypeC</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ESP32-S3 N16R8</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>SCLK</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>CS</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>DC</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>SPI_SCLK</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>SPI_MOSI</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>SPI_MISO</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>SPI_CS</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>IRQ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>IO33</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>I2C_INT</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ESP32-28</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>たぶん動く</t>
+    <rPh sb="3" eb="4">
+      <t>ウゴ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -2718,7 +2773,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -3001,6 +3056,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3008,7 +3144,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3342,55 +3478,106 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3402,65 +3589,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3797,4419 +3999,4588 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81BC7DEC-5679-4A0D-9125-1D99B7399C91}">
-  <dimension ref="A1:AA94"/>
+  <dimension ref="A1:AB95"/>
   <sheetFormatPr defaultColWidth="95.375" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="6.5" customWidth="1"/>
-    <col min="5" max="6" width="20.625" customWidth="1"/>
-    <col min="7" max="7" width="6.5" customWidth="1"/>
-    <col min="8" max="8" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.625" customWidth="1"/>
-    <col min="10" max="10" width="20.625" style="149" customWidth="1"/>
-    <col min="11" max="11" width="6.5" customWidth="1"/>
-    <col min="12" max="13" width="20.625" customWidth="1"/>
-    <col min="14" max="14" width="6.5" customWidth="1"/>
-    <col min="15" max="15" width="20.625" customWidth="1"/>
-    <col min="16" max="16" width="6.5" customWidth="1"/>
-    <col min="17" max="18" width="20.625" customWidth="1"/>
-    <col min="19" max="19" width="4.75" customWidth="1"/>
-    <col min="20" max="20" width="19.25" customWidth="1"/>
-    <col min="21" max="21" width="20.625" customWidth="1"/>
-    <col min="22" max="22" width="4.75" customWidth="1"/>
-    <col min="23" max="23" width="20.625" customWidth="1"/>
-    <col min="24" max="24" width="4.75" customWidth="1"/>
-    <col min="25" max="25" width="20.625" customWidth="1"/>
-    <col min="26" max="26" width="73.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.625" customWidth="1"/>
+    <col min="3" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="6.5" customWidth="1"/>
+    <col min="6" max="7" width="20.625" customWidth="1"/>
+    <col min="8" max="8" width="6.5" customWidth="1"/>
+    <col min="9" max="9" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.625" customWidth="1"/>
+    <col min="11" max="11" width="20.625" style="120" customWidth="1"/>
+    <col min="12" max="12" width="6.5" customWidth="1"/>
+    <col min="13" max="14" width="20.625" customWidth="1"/>
+    <col min="15" max="15" width="6.5" customWidth="1"/>
+    <col min="16" max="16" width="20.625" customWidth="1"/>
+    <col min="17" max="17" width="6.5" customWidth="1"/>
+    <col min="18" max="19" width="20.625" customWidth="1"/>
+    <col min="20" max="20" width="4.75" customWidth="1"/>
+    <col min="21" max="21" width="19.25" customWidth="1"/>
+    <col min="22" max="22" width="20.625" customWidth="1"/>
+    <col min="23" max="23" width="4.75" customWidth="1"/>
+    <col min="24" max="24" width="20.625" customWidth="1"/>
+    <col min="25" max="25" width="5.5" customWidth="1"/>
+    <col min="26" max="26" width="20.625" customWidth="1"/>
+    <col min="27" max="27" width="73.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="C1" s="170" t="s">
+        <v>314</v>
+      </c>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
+      <c r="M1" s="171">
+        <v>3.5</v>
+      </c>
+      <c r="N1" s="171"/>
+      <c r="P1" s="172" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q1" s="172"/>
+      <c r="R1" s="172"/>
+      <c r="S1" s="172"/>
+      <c r="T1" s="172"/>
+      <c r="U1" s="172"/>
+      <c r="V1" s="172"/>
+    </row>
+    <row r="2" spans="1:27" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="D1" s="96"/>
-      <c r="E1" s="13" t="s">
+      <c r="E2" s="96"/>
+      <c r="F2" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="96"/>
-      <c r="H1" s="13" t="s">
+      <c r="H2" s="96"/>
+      <c r="I2" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J2" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="J1" s="148" t="s">
+      <c r="K2" s="119" t="s">
         <v>281</v>
       </c>
-      <c r="K1" s="96"/>
-      <c r="L1" s="13" t="s">
+      <c r="L2" s="96"/>
+      <c r="M2" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="N2" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="N1" s="96"/>
-      <c r="O1" s="13" t="s">
+      <c r="O2" s="96"/>
+      <c r="P2" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="13" t="s">
+      <c r="Q2" s="96"/>
+      <c r="R2" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="S2" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="S1" s="96"/>
-      <c r="T1" s="13" t="s">
+      <c r="T2" s="96"/>
+      <c r="U2" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="V2" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="V1" s="96"/>
-      <c r="W1" s="13" t="s">
+      <c r="W2" s="96"/>
+      <c r="X2" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="X1" s="96"/>
-      <c r="Y1" s="13" t="s">
+      <c r="Y2" s="96"/>
+      <c r="Z2" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AA2" s="13" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A2" s="33" t="s">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A3" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B3" s="33"/>
+      <c r="C3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="D3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="35" t="s">
+      <c r="E3" s="78"/>
+      <c r="F3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="G3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="35" t="s">
+      <c r="H3" s="78"/>
+      <c r="I3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="J3" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="K3" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="K2" s="78"/>
-      <c r="L2" s="35" t="s">
+      <c r="L3" s="78"/>
+      <c r="M3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="M2" s="35" t="s">
+      <c r="N3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="N2" s="78"/>
-      <c r="O2" s="34" t="s">
+      <c r="O3" s="78"/>
+      <c r="P3" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="34" t="s">
+      <c r="Q3" s="78"/>
+      <c r="R3" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="R2" s="34" t="s">
+      <c r="S3" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="S2" s="78"/>
-      <c r="T2" s="34" t="s">
+      <c r="T3" s="78"/>
+      <c r="U3" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="U2" s="34" t="s">
+      <c r="V3" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="V2" s="78"/>
-      <c r="W2" s="34" t="s">
+      <c r="W3" s="78"/>
+      <c r="X3" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="35" t="s">
+      <c r="Y3" s="78"/>
+      <c r="Z3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="Z2" s="16"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A3" s="33"/>
-      <c r="B3" s="35" t="s">
+      <c r="AA3" s="16"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="D4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="D3" s="78"/>
-      <c r="E3" s="35" t="s">
+      <c r="E4" s="78"/>
+      <c r="F4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="G4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="G3" s="78"/>
-      <c r="H3" s="35" t="s">
+      <c r="H4" s="78"/>
+      <c r="I4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="J4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="K4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="K3" s="78"/>
-      <c r="L3" s="35" t="s">
+      <c r="L4" s="78"/>
+      <c r="M4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="M3" s="35" t="s">
+      <c r="N4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="N3" s="78"/>
-      <c r="O3" s="35" t="s">
+      <c r="O4" s="78"/>
+      <c r="P4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="35" t="s">
+      <c r="Q4" s="78"/>
+      <c r="R4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="R3" s="35" t="s">
+      <c r="S4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="S3" s="78"/>
-      <c r="T3" s="35" t="s">
+      <c r="T4" s="78"/>
+      <c r="U4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="U3" s="35" t="s">
+      <c r="V4" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="V3" s="78"/>
-      <c r="W3" s="77" t="s">
+      <c r="W4" s="78"/>
+      <c r="X4" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="Y4" s="78"/>
+      <c r="Z4" s="77" t="s">
         <v>221</v>
       </c>
-      <c r="X3" s="78"/>
-      <c r="Y3" s="77" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z3" s="16"/>
-    </row>
-    <row r="4" spans="1:26" ht="30" x14ac:dyDescent="0.4">
-      <c r="A4" s="33" t="s">
+      <c r="AA4" s="16"/>
+    </row>
+    <row r="5" spans="1:27" ht="30" x14ac:dyDescent="0.4">
+      <c r="A5" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="D5" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="78"/>
-      <c r="E4" s="35" t="s">
+      <c r="E5" s="78"/>
+      <c r="F5" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="G5" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="78"/>
-      <c r="H4" s="76" t="s">
+      <c r="H5" s="78"/>
+      <c r="I5" s="76" t="s">
         <v>302</v>
       </c>
-      <c r="I4" s="76" t="s">
+      <c r="J5" s="76" t="s">
         <v>211</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="K5" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="K4" s="78"/>
-      <c r="L4" s="35" t="s">
+      <c r="L5" s="78"/>
+      <c r="M5" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="M4" s="35" t="s">
+      <c r="N5" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="N4" s="78"/>
-      <c r="O4" s="76" t="s">
+      <c r="O5" s="78"/>
+      <c r="P5" s="76" t="s">
         <v>212</v>
       </c>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="34" t="s">
+      <c r="Q5" s="78"/>
+      <c r="R5" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="R4" s="34" t="s">
+      <c r="S5" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="S4" s="78"/>
-      <c r="T4" s="76" t="s">
+      <c r="T5" s="78"/>
+      <c r="U5" s="76" t="s">
         <v>212</v>
       </c>
-      <c r="U4" s="34" t="s">
+      <c r="V5" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="V4" s="78"/>
-      <c r="W4" s="34" t="s">
+      <c r="W5" s="78"/>
+      <c r="X5" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="X4" s="78"/>
-      <c r="Y4" s="35" t="s">
+      <c r="Y5" s="78"/>
+      <c r="Z5" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="Z4" s="16"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A5" s="33" t="s">
+      <c r="AA5" s="16"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A6" s="33" t="s">
         <v>282</v>
       </c>
-      <c r="B5" s="147" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="C5" s="147" t="s">
+      <c r="D6" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="D5" s="78"/>
-      <c r="E5" s="106" t="s">
+      <c r="E6" s="78"/>
+      <c r="F6" s="106" t="s">
         <v>284</v>
       </c>
-      <c r="F5" s="147" t="s">
+      <c r="G6" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="G5" s="78"/>
-      <c r="H5" s="147" t="s">
+      <c r="H6" s="78"/>
+      <c r="I6" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="I5" s="147" t="s">
+      <c r="J6" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="J5" s="106" t="s">
+      <c r="K6" s="106" t="s">
         <v>284</v>
       </c>
-      <c r="K5" s="78"/>
-      <c r="L5" s="106" t="s">
+      <c r="L6" s="78"/>
+      <c r="M6" s="106" t="s">
         <v>284</v>
       </c>
-      <c r="M5" s="147" t="s">
+      <c r="N6" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="N5" s="78"/>
-      <c r="O5" s="147" t="s">
+      <c r="O6" s="78"/>
+      <c r="P6" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="147" t="s">
+      <c r="Q6" s="78"/>
+      <c r="R6" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="R5" s="147" t="s">
+      <c r="S6" s="118" t="s">
         <v>299</v>
       </c>
-      <c r="S5" s="78"/>
-      <c r="T5" s="105" t="s">
+      <c r="T6" s="78"/>
+      <c r="U6" s="105" t="s">
         <v>283</v>
       </c>
-      <c r="U5" s="105" t="s">
+      <c r="V6" s="105" t="s">
         <v>283</v>
       </c>
-      <c r="V5" s="78"/>
-      <c r="W5" s="34"/>
-      <c r="X5" s="78"/>
-      <c r="Y5" s="35"/>
-      <c r="Z5" s="16"/>
-    </row>
-    <row r="6" spans="1:26" ht="30" x14ac:dyDescent="0.4">
-      <c r="A6" s="33" t="s">
+      <c r="W6" s="78"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="78"/>
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="16"/>
+    </row>
+    <row r="7" spans="1:27" ht="30" x14ac:dyDescent="0.4">
+      <c r="A7" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="B6" s="78"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="77" t="s">
+      <c r="B7" s="33"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="77" t="s">
         <v>217</v>
       </c>
-      <c r="I6" s="77" t="s">
+      <c r="J7" s="77" t="s">
         <v>217</v>
       </c>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="78"/>
-      <c r="N6" s="78"/>
-      <c r="O6" s="77" t="s">
+      <c r="K7" s="78"/>
+      <c r="L7" s="78"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="78"/>
+      <c r="O7" s="78"/>
+      <c r="P7" s="77" t="s">
         <v>217</v>
       </c>
-      <c r="P6" s="78"/>
-      <c r="Q6" s="77" t="s">
+      <c r="Q7" s="78"/>
+      <c r="R7" s="77" t="s">
         <v>217</v>
       </c>
-      <c r="R6" s="77" t="s">
+      <c r="S7" s="77" t="s">
         <v>217</v>
       </c>
-      <c r="S6" s="78"/>
-      <c r="T6" s="78"/>
-      <c r="U6" s="78"/>
-      <c r="V6" s="78"/>
-      <c r="W6" s="78"/>
-      <c r="X6" s="78"/>
-      <c r="Y6" s="78"/>
-      <c r="Z6" s="16"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A7" s="18" t="s">
+      <c r="T7" s="78"/>
+      <c r="U7" s="78"/>
+      <c r="V7" s="78"/>
+      <c r="W7" s="78"/>
+      <c r="X7" s="78"/>
+      <c r="Y7" s="78"/>
+      <c r="Z7" s="78"/>
+      <c r="AA7" s="16"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A8" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="D8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="97"/>
-      <c r="E7" s="12" t="s">
+      <c r="E8" s="97"/>
+      <c r="F8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="G7" s="97"/>
-      <c r="H7" s="12" t="s">
+      <c r="H8" s="97"/>
+      <c r="I8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="J8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="K8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="K7" s="97"/>
-      <c r="L7" s="12" t="s">
+      <c r="L8" s="97"/>
+      <c r="M8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="N8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="N7" s="97"/>
-      <c r="O7" s="12" t="s">
+      <c r="O8" s="97"/>
+      <c r="P8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="P7" s="97"/>
-      <c r="Q7" s="12" t="s">
+      <c r="Q8" s="97"/>
+      <c r="R8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="R7" s="12" t="s">
+      <c r="S8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="S7" s="97"/>
-      <c r="T7" s="97"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="97"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="97"/>
-      <c r="Y7" s="12" t="s">
+      <c r="T8" s="97"/>
+      <c r="U8" s="97"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="97"/>
+      <c r="X8" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="Z7" s="12"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A8" s="17" t="s">
+      <c r="Y8" s="97"/>
+      <c r="Z8" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA8" s="12"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A9" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="D9" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="97"/>
-      <c r="E8" s="40" t="s">
+      <c r="E9" s="97"/>
+      <c r="F9" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="G9" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="G8" s="97"/>
-      <c r="H8" s="40" t="s">
+      <c r="H9" s="97"/>
+      <c r="I9" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="J9" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="J8" s="40" t="s">
+      <c r="K9" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="K8" s="97"/>
-      <c r="L8" s="40" t="s">
+      <c r="L9" s="97"/>
+      <c r="M9" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="M8" s="40" t="s">
+      <c r="N9" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="N8" s="97"/>
-      <c r="O8" s="40" t="s">
+      <c r="O9" s="97"/>
+      <c r="P9" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="P8" s="97"/>
-      <c r="Q8" s="40" t="s">
+      <c r="Q9" s="97"/>
+      <c r="R9" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="R8" s="40" t="s">
+      <c r="S9" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="S8" s="97"/>
-      <c r="T8" s="97"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="97"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="97"/>
-      <c r="Y8" s="40" t="s">
+      <c r="T9" s="97"/>
+      <c r="U9" s="97"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="97"/>
+      <c r="X9" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="Z8" s="40"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A9" s="73" t="s">
+      <c r="Y9" s="97"/>
+      <c r="Z9" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA9" s="40"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A10" s="73" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="150" t="s">
+      <c r="B10" s="73"/>
+      <c r="C10" s="121" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="D10" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="97"/>
-      <c r="E9" s="74" t="s">
+      <c r="E10" s="97"/>
+      <c r="F10" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="F9" s="74" t="s">
+      <c r="G10" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="G9" s="97"/>
-      <c r="H9" s="74" t="s">
+      <c r="H10" s="97"/>
+      <c r="I10" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="I9" s="150" t="s">
+      <c r="J10" s="121" t="s">
         <v>110</v>
       </c>
-      <c r="J9" s="74" t="s">
+      <c r="K10" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="K9" s="97"/>
-      <c r="L9" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="M9" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="N9" s="97"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="97"/>
-      <c r="Q9" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="97"/>
-      <c r="T9" s="97"/>
-      <c r="U9" s="74"/>
-      <c r="V9" s="97"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="97"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="12"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A10" s="73" t="s">
-        <v>113</v>
-      </c>
-      <c r="B10" s="150" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="97"/>
-      <c r="E10" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="F10" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="97"/>
-      <c r="H10" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="I10" s="150" t="s">
-        <v>111</v>
-      </c>
-      <c r="J10" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="K10" s="97"/>
-      <c r="L10" s="74" t="s">
-        <v>110</v>
-      </c>
+      <c r="L10" s="97"/>
       <c r="M10" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="N10" s="97"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="74" t="s">
+      <c r="N10" s="74" t="s">
         <v>110</v>
       </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="97"/>
+      <c r="O10" s="97"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="97"/>
+      <c r="R10" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="S10" s="12"/>
       <c r="T10" s="97"/>
-      <c r="U10" s="74"/>
-      <c r="V10" s="97"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="97"/>
-      <c r="Y10" s="12"/>
+      <c r="U10" s="97"/>
+      <c r="V10" s="74"/>
+      <c r="W10" s="97"/>
+      <c r="X10" s="121" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y10" s="97"/>
       <c r="Z10" s="12"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A11" s="3" t="s">
+      <c r="AA10" s="12"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A11" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="73"/>
+      <c r="C11" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" s="97"/>
+      <c r="F11" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="H11" s="97"/>
+      <c r="I11" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="J11" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="K11" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="L11" s="97"/>
+      <c r="M11" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="N11" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="O11" s="97"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="97"/>
+      <c r="R11" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="S11" s="12"/>
+      <c r="T11" s="97"/>
+      <c r="U11" s="97"/>
+      <c r="V11" s="74"/>
+      <c r="W11" s="97"/>
+      <c r="X11" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y11" s="97"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="12"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A12" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B12" s="3"/>
+      <c r="C12" s="12">
         <v>2.8</v>
       </c>
-      <c r="C11" s="12">
+      <c r="D12" s="12">
         <v>2.8</v>
       </c>
-      <c r="D11" s="97"/>
-      <c r="E11" s="12">
+      <c r="E12" s="97"/>
+      <c r="F12" s="12">
         <v>2.8</v>
       </c>
-      <c r="F11" s="12">
+      <c r="G12" s="12">
         <v>2.8</v>
       </c>
-      <c r="G11" s="97"/>
-      <c r="H11" s="12">
+      <c r="H12" s="97"/>
+      <c r="I12" s="12">
         <v>2.8</v>
       </c>
-      <c r="I11" s="12">
+      <c r="J12" s="12">
         <v>2.8</v>
       </c>
-      <c r="J11" s="12">
+      <c r="K12" s="12">
         <v>2.8</v>
       </c>
-      <c r="K11" s="97"/>
-      <c r="L11" s="75">
+      <c r="L12" s="97"/>
+      <c r="M12" s="75">
         <v>3.5</v>
       </c>
-      <c r="M11" s="75">
+      <c r="N12" s="75">
         <v>3.5</v>
       </c>
-      <c r="N11" s="97"/>
-      <c r="O11" s="75">
+      <c r="O12" s="97"/>
+      <c r="P12" s="75">
         <v>3.2</v>
       </c>
-      <c r="P11" s="97"/>
-      <c r="Q11" s="75">
+      <c r="Q12" s="97"/>
+      <c r="R12" s="75">
         <v>3.5</v>
       </c>
-      <c r="R11" s="75">
+      <c r="S12" s="75">
         <v>4</v>
       </c>
-      <c r="S11" s="97"/>
-      <c r="T11" s="12">
+      <c r="T12" s="97"/>
+      <c r="U12" s="12">
         <v>2.8</v>
       </c>
-      <c r="U11" s="75">
+      <c r="V12" s="75">
         <v>3.5</v>
       </c>
-      <c r="V11" s="97"/>
-      <c r="W11" s="75">
+      <c r="W12" s="97"/>
+      <c r="X12" s="75">
         <v>2.8</v>
       </c>
-      <c r="X11" s="97"/>
-      <c r="Y11" s="75">
+      <c r="Y12" s="97"/>
+      <c r="Z12" s="75">
         <v>5</v>
       </c>
-      <c r="Z11" s="12"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A12" s="125" t="s">
+      <c r="AA12" s="12"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A13" s="134" t="s">
         <v>196</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B13" s="3"/>
+      <c r="C13" s="12">
         <v>320</v>
       </c>
-      <c r="C12" s="12">
+      <c r="D13" s="12">
         <v>320</v>
       </c>
-      <c r="D12" s="97"/>
-      <c r="E12" s="12">
+      <c r="E13" s="97"/>
+      <c r="F13" s="12">
         <v>320</v>
       </c>
-      <c r="F12" s="12">
+      <c r="G13" s="12">
         <v>320</v>
       </c>
-      <c r="G12" s="97"/>
-      <c r="H12" s="12">
+      <c r="H13" s="97"/>
+      <c r="I13" s="12">
         <v>320</v>
       </c>
-      <c r="I12" s="12">
+      <c r="J13" s="12">
         <v>320</v>
       </c>
-      <c r="J12" s="12">
+      <c r="K13" s="12">
         <v>320</v>
       </c>
-      <c r="K12" s="97"/>
-      <c r="L12" s="20">
+      <c r="L13" s="97"/>
+      <c r="M13" s="20">
         <v>480</v>
       </c>
-      <c r="M12" s="20">
+      <c r="N13" s="20">
         <v>480</v>
       </c>
-      <c r="N12" s="97"/>
-      <c r="O12" s="12">
+      <c r="O13" s="97"/>
+      <c r="P13" s="12">
         <v>320</v>
       </c>
-      <c r="P12" s="97"/>
-      <c r="Q12" s="20">
+      <c r="Q13" s="97"/>
+      <c r="R13" s="20">
         <v>480</v>
       </c>
-      <c r="R12" s="20">
+      <c r="S13" s="20">
         <v>480</v>
       </c>
-      <c r="S12" s="97"/>
-      <c r="T12" s="12">
+      <c r="T13" s="97"/>
+      <c r="U13" s="12">
         <v>320</v>
       </c>
-      <c r="U12" s="20">
+      <c r="V13" s="20">
         <v>480</v>
       </c>
-      <c r="V12" s="97"/>
-      <c r="W12" s="20"/>
-      <c r="X12" s="97"/>
-      <c r="Y12" s="20">
+      <c r="W13" s="97"/>
+      <c r="X13" s="12">
+        <v>320</v>
+      </c>
+      <c r="Y13" s="97"/>
+      <c r="Z13" s="20">
         <v>800</v>
       </c>
-      <c r="Z12" s="12"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A13" s="125"/>
-      <c r="B13" s="12">
+      <c r="AA13" s="12"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A14" s="134"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="12">
         <v>240</v>
       </c>
-      <c r="C13" s="12">
+      <c r="D14" s="12">
         <v>240</v>
       </c>
-      <c r="D13" s="97"/>
-      <c r="E13" s="12">
+      <c r="E14" s="97"/>
+      <c r="F14" s="12">
         <v>240</v>
       </c>
-      <c r="F13" s="12">
+      <c r="G14" s="12">
         <v>240</v>
       </c>
-      <c r="G13" s="97"/>
-      <c r="H13" s="12">
+      <c r="H14" s="97"/>
+      <c r="I14" s="12">
         <v>240</v>
       </c>
-      <c r="I13" s="12">
+      <c r="J14" s="12">
         <v>240</v>
       </c>
-      <c r="J13" s="12">
+      <c r="K14" s="12">
         <v>240</v>
       </c>
-      <c r="K13" s="97"/>
-      <c r="L13" s="20">
+      <c r="L14" s="97"/>
+      <c r="M14" s="20">
         <v>320</v>
       </c>
-      <c r="M13" s="20">
+      <c r="N14" s="20">
         <v>320</v>
       </c>
-      <c r="N13" s="97"/>
-      <c r="O13" s="12">
+      <c r="O14" s="97"/>
+      <c r="P14" s="12">
         <v>240</v>
       </c>
-      <c r="P13" s="97"/>
-      <c r="Q13" s="20">
+      <c r="Q14" s="97"/>
+      <c r="R14" s="20">
         <v>320</v>
       </c>
-      <c r="R13" s="20">
+      <c r="S14" s="20">
         <v>320</v>
       </c>
-      <c r="S13" s="97"/>
-      <c r="T13" s="12">
+      <c r="T14" s="97"/>
+      <c r="U14" s="12">
         <v>240</v>
       </c>
-      <c r="U13" s="20">
+      <c r="V14" s="20">
         <v>320</v>
       </c>
-      <c r="V13" s="97"/>
-      <c r="W13" s="20"/>
-      <c r="X13" s="97"/>
-      <c r="Y13" s="20">
+      <c r="W14" s="97"/>
+      <c r="X14" s="12">
+        <v>240</v>
+      </c>
+      <c r="Y14" s="97"/>
+      <c r="Z14" s="20">
         <v>480</v>
       </c>
-      <c r="Z13" s="12"/>
-    </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="126" t="s">
+      <c r="AA14" s="12"/>
+    </row>
+    <row r="15" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="123" t="s">
         <v>195</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B15" s="24"/>
+      <c r="C15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="96"/>
-      <c r="E14" s="13" t="s">
+      <c r="E15" s="96"/>
+      <c r="F15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="G15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="G14" s="96"/>
-      <c r="H14" s="13" t="s">
+      <c r="H15" s="96"/>
+      <c r="I15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="J15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="K15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="K14" s="96"/>
-      <c r="L14" s="13" t="s">
+      <c r="L15" s="96"/>
+      <c r="M15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="M14" s="13" t="s">
+      <c r="N15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="N14" s="96"/>
-      <c r="O14" s="13" t="s">
+      <c r="O15" s="96"/>
+      <c r="P15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="13" t="s">
+      <c r="Q15" s="96"/>
+      <c r="R15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="R14" s="13" t="s">
+      <c r="S15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="S14" s="96"/>
-      <c r="T14" s="13" t="s">
+      <c r="T15" s="96"/>
+      <c r="U15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="U14" s="13" t="s">
+      <c r="V15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="V14" s="96"/>
-      <c r="W14" s="13" t="s">
+      <c r="W15" s="96"/>
+      <c r="X15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="X14" s="96"/>
-      <c r="Y14" s="13" t="s">
+      <c r="Y15" s="96"/>
+      <c r="Z15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="Z14" s="2" t="s">
+      <c r="AA15" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="126"/>
-      <c r="B15" s="80" t="s">
+    <row r="16" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="123"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="C15" s="81" t="s">
+      <c r="D16" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="D15" s="98"/>
-      <c r="E15" s="81" t="s">
+      <c r="E16" s="98"/>
+      <c r="F16" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="F15" s="81" t="s">
+      <c r="G16" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="G15" s="98"/>
-      <c r="H15" s="81" t="s">
+      <c r="H16" s="98"/>
+      <c r="I16" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="I15" s="80" t="s">
+      <c r="J16" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="J15" s="81" t="s">
+      <c r="K16" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="K15" s="98"/>
-      <c r="L15" s="82" t="s">
+      <c r="L16" s="98"/>
+      <c r="M16" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="M15" s="82" t="s">
+      <c r="N16" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="N15" s="98"/>
-      <c r="O15" s="81" t="s">
+      <c r="O16" s="98"/>
+      <c r="P16" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="82" t="s">
+      <c r="Q16" s="98"/>
+      <c r="R16" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="R15" s="82" t="s">
+      <c r="S16" s="82" t="s">
         <v>205</v>
       </c>
-      <c r="S15" s="98"/>
-      <c r="T15" s="80" t="s">
+      <c r="T16" s="98"/>
+      <c r="U16" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="U15" s="82" t="s">
+      <c r="V16" s="82" t="s">
         <v>287</v>
       </c>
-      <c r="V15" s="98"/>
-      <c r="W15" s="80" t="s">
+      <c r="W16" s="98"/>
+      <c r="X16" s="80" t="s">
         <v>199</v>
       </c>
-      <c r="X15" s="98"/>
-      <c r="Y15" s="82" t="s">
+      <c r="Y16" s="98"/>
+      <c r="Z16" s="82" t="s">
         <v>238</v>
       </c>
-      <c r="Z15" s="2"/>
-    </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="126"/>
-      <c r="B16" s="80" t="s">
+      <c r="AA16" s="2"/>
+    </row>
+    <row r="17" spans="1:28" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="123"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="81" t="s">
+      <c r="D17" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="98"/>
-      <c r="E16" s="81" t="s">
+      <c r="E17" s="98"/>
+      <c r="F17" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="F16" s="81" t="s">
+      <c r="G17" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="98"/>
-      <c r="H16" s="81" t="s">
+      <c r="H17" s="98"/>
+      <c r="I17" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="I16" s="83" t="s">
+      <c r="J17" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="J16" s="81" t="s">
+      <c r="K17" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="K16" s="98"/>
-      <c r="L16" s="81" t="s">
+      <c r="L17" s="98"/>
+      <c r="M17" s="81" t="s">
         <v>301</v>
       </c>
-      <c r="M16" s="81" t="s">
+      <c r="N17" s="81" t="s">
         <v>300</v>
       </c>
-      <c r="N16" s="98"/>
-      <c r="O16" s="81" t="s">
+      <c r="O17" s="98"/>
+      <c r="P17" s="81" t="s">
         <v>82</v>
       </c>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="81" t="s">
+      <c r="Q17" s="98"/>
+      <c r="R17" s="81" t="s">
         <v>278</v>
       </c>
-      <c r="R16" s="81" t="s">
+      <c r="S17" s="81" t="s">
         <v>278</v>
       </c>
-      <c r="S16" s="98"/>
-      <c r="T16" s="83" t="s">
+      <c r="T17" s="98"/>
+      <c r="U17" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="U16" s="82" t="s">
+      <c r="V17" s="82" t="s">
         <v>287</v>
       </c>
-      <c r="V16" s="98"/>
-      <c r="W16" s="80" t="s">
+      <c r="W17" s="98"/>
+      <c r="X17" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="X16" s="98"/>
-      <c r="Y16" s="21" t="s">
+      <c r="Y17" s="98"/>
+      <c r="Z17" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="Z16" s="2"/>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A17" s="126"/>
-      <c r="B17" s="79" t="s">
+      <c r="AA17" s="2"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A18" s="123"/>
+      <c r="B18" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="79" t="s">
+      <c r="D18" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="99"/>
-      <c r="E17" s="79" t="s">
+      <c r="E18" s="99"/>
+      <c r="F18" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="79" t="s">
+      <c r="G18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="99"/>
-      <c r="H17" s="79" t="s">
+      <c r="H18" s="99"/>
+      <c r="I18" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="I17" s="79" t="s">
+      <c r="J18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="J17" s="79" t="s">
+      <c r="K18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="K17" s="99"/>
-      <c r="L17" s="79" t="s">
+      <c r="L18" s="99"/>
+      <c r="M18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="M17" s="79" t="s">
+      <c r="N18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="N17" s="99"/>
-      <c r="O17" s="79" t="s">
+      <c r="O18" s="99"/>
+      <c r="P18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="P17" s="99"/>
-      <c r="Q17" s="79" t="s">
+      <c r="Q18" s="99"/>
+      <c r="R18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="R17" s="79" t="s">
+      <c r="S18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="S17" s="99"/>
-      <c r="T17" s="79" t="s">
+      <c r="T18" s="99"/>
+      <c r="U18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="U17" s="79" t="s">
+      <c r="V18" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="V17" s="99"/>
-      <c r="W17" s="84" t="s">
+      <c r="W18" s="99"/>
+      <c r="X18" s="84" t="s">
         <v>223</v>
       </c>
-      <c r="X17" s="99"/>
-      <c r="Y17" s="113" t="s">
+      <c r="Y18" s="99"/>
+      <c r="Z18" s="152" t="s">
         <v>239</v>
       </c>
-      <c r="Z17" s="7" t="s">
+      <c r="AA18" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB18" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A18" s="126"/>
-      <c r="B18" s="112" t="s">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A19" s="123"/>
+      <c r="B19" s="134" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="112" t="s">
+      <c r="D19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="99"/>
-      <c r="E18" s="112" t="s">
+      <c r="E19" s="99"/>
+      <c r="F19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="F18" s="112" t="s">
+      <c r="G19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="99"/>
-      <c r="H18" s="112" t="s">
+      <c r="H19" s="99"/>
+      <c r="I19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="I18" s="112" t="s">
+      <c r="J19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="J18" s="112" t="s">
+      <c r="K19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="99"/>
-      <c r="L18" s="112" t="s">
+      <c r="L19" s="99"/>
+      <c r="M19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="112" t="s">
+      <c r="N19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="99"/>
-      <c r="O18" s="112" t="s">
+      <c r="O19" s="99"/>
+      <c r="P19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="99"/>
-      <c r="Q18" s="112" t="s">
+      <c r="Q19" s="99"/>
+      <c r="R19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="112" t="s">
+      <c r="S19" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="99"/>
-      <c r="T18" s="120" t="s">
+      <c r="T19" s="99"/>
+      <c r="U19" s="148" t="s">
         <v>286</v>
       </c>
-      <c r="U18" s="120" t="s">
+      <c r="V19" s="148" t="s">
         <v>286</v>
       </c>
-      <c r="V18" s="99"/>
-      <c r="W18" s="116" t="s">
+      <c r="W19" s="99"/>
+      <c r="X19" s="150" t="s">
         <v>224</v>
       </c>
-      <c r="X18" s="99"/>
-      <c r="Y18" s="114"/>
-      <c r="Z18" s="7" t="s">
+      <c r="Y19" s="99"/>
+      <c r="Z19" s="153"/>
+      <c r="AA19" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A19" s="126"/>
-      <c r="B19" s="112"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="99"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="99"/>
-      <c r="T19" s="121"/>
-      <c r="U19" s="121"/>
-      <c r="V19" s="99"/>
-      <c r="W19" s="117"/>
-      <c r="X19" s="99"/>
-      <c r="Y19" s="114"/>
-      <c r="Z19" s="10" t="s">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A20" s="123"/>
+      <c r="B20" s="134"/>
+      <c r="C20" s="131"/>
+      <c r="D20" s="131"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="131"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="99"/>
+      <c r="I20" s="131"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="131"/>
+      <c r="L20" s="99"/>
+      <c r="M20" s="131"/>
+      <c r="N20" s="131"/>
+      <c r="O20" s="99"/>
+      <c r="P20" s="131"/>
+      <c r="Q20" s="99"/>
+      <c r="R20" s="131"/>
+      <c r="S20" s="131"/>
+      <c r="T20" s="99"/>
+      <c r="U20" s="149"/>
+      <c r="V20" s="149"/>
+      <c r="W20" s="99"/>
+      <c r="X20" s="151"/>
+      <c r="Y20" s="99"/>
+      <c r="Z20" s="153"/>
+      <c r="AA20" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AB20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A20" s="126"/>
-      <c r="B20" s="8" t="s">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A21" s="123"/>
+      <c r="B21" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="99"/>
-      <c r="E20" s="8" t="s">
+      <c r="E21" s="99"/>
+      <c r="F21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="G20" s="99"/>
-      <c r="H20" s="8" t="s">
+      <c r="H21" s="99"/>
+      <c r="I21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="J21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="K20" s="99"/>
-      <c r="L20" s="8" t="s">
+      <c r="L21" s="99"/>
+      <c r="M21" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="M20" s="8" t="s">
+      <c r="N21" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="N20" s="99"/>
-      <c r="O20" s="8" t="s">
+      <c r="O21" s="99"/>
+      <c r="P21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="99"/>
-      <c r="Q20" s="8" t="s">
+      <c r="Q21" s="99"/>
+      <c r="R21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="R20" s="8" t="s">
+      <c r="S21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="S20" s="99"/>
-      <c r="T20" s="8" t="s">
+      <c r="T21" s="99"/>
+      <c r="U21" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="U20" s="8" t="s">
+      <c r="V21" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="V20" s="99"/>
-      <c r="W20" s="11">
+      <c r="W21" s="99"/>
+      <c r="X21" s="11">
         <v>12</v>
       </c>
-      <c r="X20" s="99"/>
-      <c r="Y20" s="114"/>
-      <c r="Z20" s="7" t="s">
+      <c r="Y21" s="99"/>
+      <c r="Z21" s="153"/>
+      <c r="AA21" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A21" s="126"/>
-      <c r="B21" s="8" t="s">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A22" s="123"/>
+      <c r="B22" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="D22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="99"/>
-      <c r="E21" s="8" t="s">
+      <c r="E22" s="99"/>
+      <c r="F22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="99"/>
-      <c r="H21" s="8" t="s">
+      <c r="H22" s="99"/>
+      <c r="I22" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="J22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="K22" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="K21" s="99"/>
-      <c r="L21" s="8" t="s">
+      <c r="L22" s="99"/>
+      <c r="M22" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="M21" s="8" t="s">
+      <c r="N22" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="N21" s="99"/>
-      <c r="O21" s="8" t="s">
+      <c r="O22" s="99"/>
+      <c r="P22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="P21" s="99"/>
-      <c r="Q21" s="8" t="s">
+      <c r="Q22" s="99"/>
+      <c r="R22" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="R21" s="8" t="s">
+      <c r="S22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="S21" s="99"/>
-      <c r="T21" s="8" t="s">
+      <c r="T22" s="99"/>
+      <c r="U22" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="U21" s="8" t="s">
+      <c r="V22" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="V21" s="99"/>
-      <c r="W21" s="11">
+      <c r="W22" s="99"/>
+      <c r="X22" s="11">
         <v>11</v>
       </c>
-      <c r="X21" s="99"/>
-      <c r="Y21" s="114"/>
-      <c r="Z21" s="7" t="s">
+      <c r="Y22" s="99"/>
+      <c r="Z22" s="153"/>
+      <c r="AA22" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A22" s="126"/>
-      <c r="B22" s="8" t="s">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A23" s="123"/>
+      <c r="B23" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="99"/>
-      <c r="E22" s="8" t="s">
+      <c r="E23" s="99"/>
+      <c r="F23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="G23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="99"/>
-      <c r="H22" s="8" t="s">
+      <c r="H23" s="99"/>
+      <c r="I23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="J23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="K23" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="K22" s="99"/>
-      <c r="L22" s="8" t="s">
+      <c r="L23" s="99"/>
+      <c r="M23" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="M22" s="8" t="s">
+      <c r="N23" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="N22" s="99"/>
-      <c r="O22" s="8" t="s">
+      <c r="O23" s="99"/>
+      <c r="P23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="P22" s="99"/>
-      <c r="Q22" s="8" t="s">
+      <c r="Q23" s="99"/>
+      <c r="R23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="R22" s="8" t="s">
+      <c r="S23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="S22" s="99"/>
-      <c r="T22" s="8" t="s">
+      <c r="T23" s="99"/>
+      <c r="U23" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="U22" s="8" t="s">
+      <c r="V23" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="V22" s="99"/>
-      <c r="W22" s="11">
+      <c r="W23" s="99"/>
+      <c r="X23" s="11">
         <v>13</v>
       </c>
-      <c r="X22" s="99"/>
-      <c r="Y22" s="114"/>
-      <c r="Z22" s="7" t="s">
+      <c r="Y23" s="99"/>
+      <c r="Z23" s="153"/>
+      <c r="AA23" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A23" s="126"/>
-      <c r="B23" s="8" t="s">
+    <row r="24" spans="1:28" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="A24" s="123"/>
+      <c r="B24" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="99"/>
-      <c r="E23" s="8" t="s">
+      <c r="E24" s="99"/>
+      <c r="F24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="G24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G23" s="99"/>
-      <c r="H23" s="8" t="s">
+      <c r="H24" s="99"/>
+      <c r="I24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="J24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="K24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="99"/>
-      <c r="L23" s="8" t="s">
+      <c r="L24" s="99"/>
+      <c r="M24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="8" t="s">
+      <c r="N24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="N23" s="99"/>
-      <c r="O23" s="8" t="s">
+      <c r="O24" s="99"/>
+      <c r="P24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="P23" s="99"/>
-      <c r="Q23" s="8" t="s">
+      <c r="Q24" s="99"/>
+      <c r="R24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R23" s="8" t="s">
+      <c r="S24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="S23" s="99"/>
-      <c r="T23" s="8" t="s">
+      <c r="T24" s="99"/>
+      <c r="U24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="U23" s="8" t="s">
+      <c r="V24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="V23" s="99"/>
-      <c r="W23" s="8" t="s">
+      <c r="W24" s="99"/>
+      <c r="X24" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="X23" s="99"/>
-      <c r="Y23" s="114"/>
-      <c r="Z23" s="7" t="s">
+      <c r="Y24" s="99"/>
+      <c r="Z24" s="153"/>
+      <c r="AA24" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A24" s="126"/>
-      <c r="B24" s="8">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A25" s="123"/>
+      <c r="B25" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="C25" s="8">
         <v>40000000</v>
       </c>
-      <c r="C24" s="8">
+      <c r="D25" s="8">
         <v>40000000</v>
       </c>
-      <c r="D24" s="99"/>
-      <c r="E24" s="11">
+      <c r="E25" s="99"/>
+      <c r="F25" s="11">
         <v>55000000</v>
       </c>
-      <c r="F24" s="11">
+      <c r="G25" s="11">
         <v>55000000</v>
       </c>
-      <c r="G24" s="99"/>
-      <c r="H24" s="8">
+      <c r="H25" s="99"/>
+      <c r="I25" s="8">
         <v>40000000</v>
       </c>
-      <c r="I24" s="8">
+      <c r="J25" s="8">
         <v>40000000</v>
       </c>
-      <c r="J24" s="8">
+      <c r="K25" s="8">
         <v>40000000</v>
       </c>
-      <c r="K24" s="99"/>
-      <c r="L24" s="8">
+      <c r="L25" s="99"/>
+      <c r="M25" s="8">
         <v>40000000</v>
       </c>
-      <c r="M24" s="8">
+      <c r="N25" s="8">
         <v>40000000</v>
       </c>
-      <c r="N24" s="99"/>
-      <c r="O24" s="8">
+      <c r="O25" s="99"/>
+      <c r="P25" s="8">
         <v>40000000</v>
       </c>
-      <c r="P24" s="99"/>
-      <c r="Q24" s="8">
+      <c r="Q25" s="99"/>
+      <c r="R25" s="8">
         <v>40000000</v>
       </c>
-      <c r="R24" s="8">
+      <c r="S25" s="8">
         <v>40000000</v>
       </c>
-      <c r="S24" s="99"/>
-      <c r="T24" s="8">
+      <c r="T25" s="99"/>
+      <c r="U25" s="8">
         <v>40000000</v>
       </c>
-      <c r="U24" s="8">
+      <c r="V25" s="8">
         <v>40000000</v>
       </c>
-      <c r="V24" s="99"/>
-      <c r="W24" s="8">
+      <c r="W25" s="99"/>
+      <c r="X25" s="8">
         <v>40000000</v>
       </c>
-      <c r="X24" s="99"/>
-      <c r="Y24" s="114"/>
-      <c r="Z24" s="7" t="s">
+      <c r="Y25" s="99"/>
+      <c r="Z25" s="153"/>
+      <c r="AA25" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A25" s="126"/>
-      <c r="B25" s="8">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A26" s="123"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="8">
         <v>20000000</v>
       </c>
-      <c r="C25" s="8">
+      <c r="D26" s="8">
         <v>20000000</v>
       </c>
-      <c r="D25" s="99"/>
-      <c r="E25" s="11">
+      <c r="E26" s="99"/>
+      <c r="F26" s="11">
         <v>20000000</v>
       </c>
-      <c r="F25" s="11">
+      <c r="G26" s="11">
         <v>20000000</v>
       </c>
-      <c r="G25" s="99"/>
-      <c r="H25" s="8">
+      <c r="H26" s="99"/>
+      <c r="I26" s="8">
         <v>20000000</v>
       </c>
-      <c r="I25" s="8">
+      <c r="J26" s="8">
         <v>20000000</v>
       </c>
-      <c r="J25" s="8">
+      <c r="K26" s="8">
         <v>20000000</v>
       </c>
-      <c r="K25" s="99"/>
-      <c r="L25" s="8">
+      <c r="L26" s="99"/>
+      <c r="M26" s="8">
         <v>16000000</v>
       </c>
-      <c r="M25" s="8">
+      <c r="N26" s="8">
         <v>16000000</v>
       </c>
-      <c r="N25" s="99"/>
-      <c r="O25" s="8">
+      <c r="O26" s="99"/>
+      <c r="P26" s="8">
         <v>20000000</v>
       </c>
-      <c r="P25" s="99"/>
-      <c r="Q25" s="8">
+      <c r="Q26" s="99"/>
+      <c r="R26" s="8">
         <v>20000000</v>
       </c>
-      <c r="R25" s="8">
+      <c r="S26" s="8">
         <v>20000000</v>
       </c>
-      <c r="S25" s="99"/>
-      <c r="T25" s="8">
+      <c r="T26" s="99"/>
+      <c r="U26" s="8">
         <v>20000000</v>
       </c>
-      <c r="U25" s="8">
+      <c r="V26" s="8">
         <v>20000000</v>
       </c>
-      <c r="V25" s="99"/>
-      <c r="W25" s="8">
+      <c r="W26" s="99"/>
+      <c r="X26" s="8">
         <v>20000000</v>
       </c>
-      <c r="X25" s="99"/>
-      <c r="Y25" s="114"/>
-      <c r="Z25" s="7" t="s">
+      <c r="Y26" s="99"/>
+      <c r="Z26" s="153"/>
+      <c r="AA26" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A26" s="127"/>
-      <c r="B26" s="8">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A27" s="124"/>
+      <c r="B27" s="111"/>
+      <c r="C27" s="8">
         <v>2500000</v>
       </c>
-      <c r="C26" s="8">
+      <c r="D27" s="8">
         <v>2500000</v>
       </c>
-      <c r="D26" s="99"/>
-      <c r="E26" s="11">
+      <c r="E27" s="99"/>
+      <c r="F27" s="11">
         <v>2500000</v>
       </c>
-      <c r="F26" s="11">
+      <c r="G27" s="11">
         <v>2500000</v>
       </c>
-      <c r="G26" s="99"/>
-      <c r="H26" s="8">
+      <c r="H27" s="99"/>
+      <c r="I27" s="8">
         <v>2500000</v>
       </c>
-      <c r="I26" s="8">
+      <c r="J27" s="8">
         <v>2500000</v>
       </c>
-      <c r="J26" s="8">
+      <c r="K27" s="8">
         <v>2500000</v>
       </c>
-      <c r="K26" s="99"/>
-      <c r="L26" s="8">
+      <c r="L27" s="99"/>
+      <c r="M27" s="8">
         <v>2500000</v>
       </c>
-      <c r="M26" s="8">
+      <c r="N27" s="8">
         <v>2500000</v>
       </c>
-      <c r="N26" s="99"/>
-      <c r="O26" s="8">
+      <c r="O27" s="99"/>
+      <c r="P27" s="8">
         <v>2500000</v>
       </c>
-      <c r="P26" s="99"/>
-      <c r="Q26" s="8">
+      <c r="Q27" s="99"/>
+      <c r="R27" s="8">
         <v>2500000</v>
       </c>
-      <c r="R26" s="8">
+      <c r="S27" s="8">
         <v>2500000</v>
       </c>
-      <c r="S26" s="99"/>
-      <c r="T26" s="8">
+      <c r="T27" s="99"/>
+      <c r="U27" s="8">
         <v>2500000</v>
       </c>
-      <c r="U26" s="8">
+      <c r="V27" s="8">
         <v>2500000</v>
       </c>
-      <c r="V26" s="99"/>
-      <c r="W26" s="8">
+      <c r="W27" s="99"/>
+      <c r="X27" s="8">
         <v>2500000</v>
       </c>
-      <c r="X26" s="99"/>
-      <c r="Y26" s="115"/>
-      <c r="Z26" s="7" t="s">
+      <c r="Y27" s="99"/>
+      <c r="Z27" s="154"/>
+      <c r="AA27" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A27" s="24" t="s">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A28" s="122" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="71" t="s">
+      <c r="B28" s="168"/>
+      <c r="C28" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="71" t="s">
+      <c r="D28" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="100"/>
-      <c r="E27" s="29" t="s">
+      <c r="E28" s="100"/>
+      <c r="F28" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="G28" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="G27" s="100"/>
-      <c r="H27" s="71" t="s">
+      <c r="H28" s="100"/>
+      <c r="I28" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="I27" s="71" t="s">
+      <c r="J28" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="J27" s="71" t="s">
+      <c r="K28" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="K27" s="100"/>
-      <c r="L27" s="29" t="s">
+      <c r="L28" s="100"/>
+      <c r="M28" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="M27" s="29" t="s">
+      <c r="N28" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="N27" s="100"/>
-      <c r="O27" s="36" t="s">
+      <c r="O28" s="100"/>
+      <c r="P28" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="P27" s="100"/>
-      <c r="Q27" s="36" t="s">
+      <c r="Q28" s="100"/>
+      <c r="R28" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="R27" s="36" t="s">
+      <c r="S28" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="S27" s="100"/>
-      <c r="T27" s="107" t="s">
+      <c r="T28" s="100"/>
+      <c r="U28" s="107" t="s">
         <v>62</v>
       </c>
-      <c r="U27" s="107" t="s">
+      <c r="V28" s="107" t="s">
         <v>62</v>
       </c>
-      <c r="V27" s="100"/>
-      <c r="W27" s="85" t="s">
+      <c r="W28" s="100"/>
+      <c r="X28" s="85" t="s">
         <v>226</v>
       </c>
-      <c r="X27" s="100"/>
-      <c r="Y27" s="36"/>
-      <c r="Z27" s="7" t="s">
+      <c r="Y28" s="100"/>
+      <c r="Z28" s="36"/>
+      <c r="AA28" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="133" t="s">
+    <row r="29" spans="1:28" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="122" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="158"/>
+      <c r="C29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="96"/>
-      <c r="E28" s="4" t="s">
+      <c r="E29" s="96"/>
+      <c r="F29" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G28" s="96"/>
-      <c r="H28" s="2" t="s">
+      <c r="H29" s="96"/>
+      <c r="I29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="K29" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="K28" s="96"/>
-      <c r="L28" s="4" t="s">
+      <c r="L29" s="96"/>
+      <c r="M29" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="N28" s="96"/>
-      <c r="O28" s="2" t="s">
+      <c r="O29" s="96"/>
+      <c r="P29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="P28" s="96"/>
-      <c r="Q28" s="2" t="s">
+      <c r="Q29" s="96"/>
+      <c r="R29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="R28" s="2" t="s">
+      <c r="S29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="S28" s="96"/>
-      <c r="T28" s="2" t="s">
+      <c r="T29" s="96"/>
+      <c r="U29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="U28" s="2" t="s">
+      <c r="V29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="V28" s="96"/>
-      <c r="W28" s="4" t="s">
+      <c r="W29" s="96"/>
+      <c r="X29" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="X28" s="96"/>
-      <c r="Y28" s="2"/>
-      <c r="Z28" s="7"/>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A29" s="126"/>
-      <c r="B29" s="16" t="s">
+      <c r="Y29" s="96"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="7"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A30" s="123"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="D30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="101"/>
-      <c r="E29" s="19" t="s">
+      <c r="E30" s="101"/>
+      <c r="F30" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="G30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="G29" s="101"/>
-      <c r="H29" s="16" t="s">
+      <c r="H30" s="101"/>
+      <c r="I30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="I29" s="16" t="s">
+      <c r="J30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="J29" s="19" t="s">
+      <c r="K30" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="K29" s="101"/>
-      <c r="L29" s="19" t="s">
+      <c r="L30" s="101"/>
+      <c r="M30" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="M29" s="16" t="s">
+      <c r="N30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="N29" s="101"/>
-      <c r="O29" s="16" t="s">
+      <c r="O30" s="101"/>
+      <c r="P30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="P29" s="101"/>
-      <c r="Q29" s="16" t="s">
+      <c r="Q30" s="101"/>
+      <c r="R30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="R29" s="16" t="s">
+      <c r="S30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="S29" s="101"/>
-      <c r="T29" s="16" t="s">
+      <c r="T30" s="101"/>
+      <c r="U30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="U29" s="16" t="s">
+      <c r="V30" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="V29" s="101"/>
-      <c r="W29" s="19" t="s">
+      <c r="W30" s="101"/>
+      <c r="X30" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="X29" s="101"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="7"/>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A30" s="126"/>
-      <c r="B30" s="5" t="s">
+      <c r="Y30" s="101"/>
+      <c r="Z30" s="16"/>
+      <c r="AA30" s="7"/>
+    </row>
+    <row r="31" spans="1:28" ht="30" x14ac:dyDescent="0.4">
+      <c r="A31" s="123"/>
+      <c r="B31" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="99"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="29" t="s">
+      <c r="E31" s="99"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="99"/>
-      <c r="H30" s="5" t="s">
+      <c r="H31" s="99"/>
+      <c r="I31" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="J31" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="6"/>
-      <c r="K30" s="99"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="29" t="s">
+      <c r="K31" s="6"/>
+      <c r="L31" s="99"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="N30" s="99"/>
-      <c r="O30" s="29" t="s">
+      <c r="O31" s="99"/>
+      <c r="P31" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P30" s="99"/>
-      <c r="Q30" s="29" t="s">
+      <c r="Q31" s="99"/>
+      <c r="R31" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="R30" s="29" t="s">
+      <c r="S31" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="S30" s="99"/>
-      <c r="T30" s="29" t="s">
+      <c r="T31" s="99"/>
+      <c r="U31" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="U30" s="29" t="s">
+      <c r="V31" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="V30" s="99"/>
-      <c r="W30" s="29"/>
-      <c r="X30" s="99"/>
-      <c r="Y30" s="29"/>
-      <c r="Z30" s="7" t="s">
+      <c r="W31" s="99"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="99"/>
+      <c r="Z31" s="29"/>
+      <c r="AA31" s="7" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A31" s="126"/>
-      <c r="B31" s="8" t="s">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.4">
+      <c r="A32" s="123"/>
+      <c r="B32" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="D32" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="99"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="29" t="s">
+      <c r="E32" s="99"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="99"/>
-      <c r="H31" s="8" t="s">
+      <c r="H32" s="99"/>
+      <c r="I32" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="J32" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J31" s="6"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="29" t="s">
+      <c r="K32" s="6"/>
+      <c r="L32" s="99"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="N31" s="99"/>
-      <c r="O31" s="29" t="s">
+      <c r="O32" s="99"/>
+      <c r="P32" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="P31" s="99"/>
-      <c r="Q31" s="29" t="s">
+      <c r="Q32" s="99"/>
+      <c r="R32" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="R31" s="29" t="s">
+      <c r="S32" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="S31" s="99"/>
-      <c r="T31" s="29" t="s">
+      <c r="T32" s="99"/>
+      <c r="U32" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="U31" s="29" t="s">
+      <c r="V32" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="V31" s="99"/>
-      <c r="W31" s="29"/>
-      <c r="X31" s="99"/>
-      <c r="Y31" s="29"/>
-      <c r="Z31" s="7" t="s">
+      <c r="W32" s="99"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="99"/>
+      <c r="Z32" s="29"/>
+      <c r="AA32" s="7" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.4">
-      <c r="A32" s="126"/>
-      <c r="B32" s="8" t="s">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A33" s="123"/>
+      <c r="B33" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="D33" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="99"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="29" t="s">
+      <c r="E33" s="99"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="G32" s="99"/>
-      <c r="H32" s="8" t="s">
+      <c r="H33" s="99"/>
+      <c r="I33" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="J33" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J32" s="6"/>
-      <c r="K32" s="99"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="29" t="s">
+      <c r="K33" s="6"/>
+      <c r="L33" s="99"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="N32" s="99"/>
-      <c r="O32" s="29" t="s">
+      <c r="O33" s="99"/>
+      <c r="P33" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="P32" s="99"/>
-      <c r="Q32" s="29" t="s">
+      <c r="Q33" s="99"/>
+      <c r="R33" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="R32" s="29" t="s">
+      <c r="S33" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="S32" s="99"/>
-      <c r="T32" s="29" t="s">
+      <c r="T33" s="99"/>
+      <c r="U33" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="U32" s="29" t="s">
+      <c r="V33" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="V32" s="99"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="99"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="7" t="s">
+      <c r="W33" s="99"/>
+      <c r="X33" s="29"/>
+      <c r="Y33" s="99"/>
+      <c r="Z33" s="29"/>
+      <c r="AA33" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A33" s="126"/>
-      <c r="B33" s="8" t="s">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A34" s="123"/>
+      <c r="B34" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="D34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="99"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="8" t="s">
+      <c r="E34" s="99"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="99"/>
-      <c r="H33" s="8" t="s">
+      <c r="H34" s="99"/>
+      <c r="I34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="J34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J33" s="9"/>
-      <c r="K33" s="99"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="8" t="s">
+      <c r="K34" s="9"/>
+      <c r="L34" s="99"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="N33" s="99"/>
-      <c r="O33" s="8" t="s">
+      <c r="O34" s="99"/>
+      <c r="P34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="P33" s="99"/>
-      <c r="Q33" s="8" t="s">
+      <c r="Q34" s="99"/>
+      <c r="R34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="R33" s="8" t="s">
+      <c r="S34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="S33" s="99"/>
-      <c r="T33" s="8" t="s">
+      <c r="T34" s="99"/>
+      <c r="U34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="U33" s="8" t="s">
+      <c r="V34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="V33" s="99"/>
-      <c r="W33" s="8"/>
-      <c r="X33" s="99"/>
-      <c r="Y33" s="8"/>
-      <c r="Z33" s="7" t="s">
+      <c r="W34" s="99"/>
+      <c r="X34" s="8"/>
+      <c r="Y34" s="99"/>
+      <c r="Z34" s="8"/>
+      <c r="AA34" s="7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A34" s="126"/>
-      <c r="B34" s="112" t="s">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A35" s="123"/>
+      <c r="B35" s="169" t="s">
+        <v>311</v>
+      </c>
+      <c r="C35" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="131" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="112" t="s">
+      <c r="E35" s="99"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="148" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" s="99"/>
+      <c r="I35" s="131" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="99"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="120" t="s">
+      <c r="J35" s="131" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" s="9"/>
+      <c r="L35" s="99"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="99"/>
-      <c r="H34" s="112" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="112" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" s="9"/>
-      <c r="K34" s="99"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="120" t="s">
+      <c r="O35" s="99"/>
+      <c r="P35" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="N34" s="99"/>
-      <c r="O34" s="120" t="s">
+      <c r="Q35" s="99"/>
+      <c r="R35" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="P34" s="99"/>
-      <c r="Q34" s="120" t="s">
+      <c r="S35" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="R34" s="120" t="s">
+      <c r="T35" s="99"/>
+      <c r="U35" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="S34" s="99"/>
-      <c r="T34" s="120" t="s">
+      <c r="V35" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="U34" s="120" t="s">
+      <c r="W35" s="99"/>
+      <c r="X35" s="22"/>
+      <c r="Y35" s="99"/>
+      <c r="Z35" s="148"/>
+      <c r="AA35" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A36" s="123"/>
+      <c r="B36" s="169"/>
+      <c r="C36" s="131"/>
+      <c r="D36" s="131"/>
+      <c r="E36" s="99"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="149"/>
+      <c r="H36" s="99"/>
+      <c r="I36" s="131"/>
+      <c r="J36" s="131"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="99"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="149"/>
+      <c r="O36" s="99"/>
+      <c r="P36" s="149"/>
+      <c r="Q36" s="99"/>
+      <c r="R36" s="149"/>
+      <c r="S36" s="149"/>
+      <c r="T36" s="99"/>
+      <c r="U36" s="149"/>
+      <c r="V36" s="149"/>
+      <c r="W36" s="99"/>
+      <c r="X36" s="23"/>
+      <c r="Y36" s="99"/>
+      <c r="Z36" s="149"/>
+      <c r="AA36" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A37" s="123"/>
+      <c r="B37" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="L37" s="99"/>
+      <c r="M37" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="V34" s="99"/>
-      <c r="W34" s="22"/>
-      <c r="X34" s="99"/>
-      <c r="Y34" s="120"/>
-      <c r="Z34" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A35" s="126"/>
-      <c r="B35" s="112"/>
-      <c r="C35" s="112"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="121"/>
-      <c r="G35" s="99"/>
-      <c r="H35" s="112"/>
-      <c r="I35" s="112"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="99"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="121"/>
-      <c r="N35" s="99"/>
-      <c r="O35" s="121"/>
-      <c r="P35" s="99"/>
-      <c r="Q35" s="121"/>
-      <c r="R35" s="121"/>
-      <c r="S35" s="99"/>
-      <c r="T35" s="121"/>
-      <c r="U35" s="121"/>
-      <c r="V35" s="99"/>
-      <c r="W35" s="23"/>
-      <c r="X35" s="99"/>
-      <c r="Y35" s="121"/>
-      <c r="Z35" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A36" s="126"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="99"/>
-      <c r="E36" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="99"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="K36" s="99"/>
-      <c r="L36" s="95" t="s">
-        <v>73</v>
-      </c>
-      <c r="M36" s="6"/>
-      <c r="N36" s="99"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="99"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
-      <c r="S36" s="99"/>
-      <c r="T36" s="99"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="99"/>
-      <c r="W36" s="11" t="s">
+      <c r="N37" s="6"/>
+      <c r="O37" s="99"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="99"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="99"/>
+      <c r="U37" s="99"/>
+      <c r="V37" s="6"/>
+      <c r="W37" s="99"/>
+      <c r="X37" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="X36" s="99"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="12" t="s">
+      <c r="Y37" s="99"/>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="12" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A37" s="126"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="29" t="s">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A38" s="123"/>
+      <c r="B38" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="29" t="s">
+      <c r="G38" s="6"/>
+      <c r="H38" s="99"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="K37" s="99"/>
-      <c r="L37" s="29" t="s">
+      <c r="L38" s="99"/>
+      <c r="M38" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="6"/>
-      <c r="N37" s="99"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="99"/>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="99"/>
-      <c r="T37" s="99"/>
-      <c r="U37" s="6">
+      <c r="N38" s="6"/>
+      <c r="O38" s="99"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="99"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="99"/>
+      <c r="U38" s="99"/>
+      <c r="V38" s="6">
         <v>2</v>
       </c>
-      <c r="V37" s="99"/>
-      <c r="W37" s="11" t="s">
+      <c r="W38" s="99"/>
+      <c r="X38" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="X37" s="99"/>
-      <c r="Y37" s="9"/>
-      <c r="Z37" s="12" t="s">
+      <c r="Y38" s="99"/>
+      <c r="Z38" s="9"/>
+      <c r="AA38" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A38" s="126"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="97"/>
-      <c r="E38" s="29" t="s">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A39" s="123"/>
+      <c r="B39" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="97"/>
+      <c r="F39" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="97"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="29" t="s">
+      <c r="G39" s="6"/>
+      <c r="H39" s="97"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="L39" s="97"/>
+      <c r="M39" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="K38" s="97"/>
-      <c r="L38" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="M38" s="6"/>
-      <c r="N38" s="97"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="97"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="97"/>
-      <c r="T38" s="97"/>
-      <c r="U38" s="6">
+      <c r="N39" s="6"/>
+      <c r="O39" s="97"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="97"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="6"/>
+      <c r="T39" s="97"/>
+      <c r="U39" s="97"/>
+      <c r="V39" s="6">
         <v>1</v>
       </c>
-      <c r="V38" s="97"/>
-      <c r="W38" s="86" t="s">
+      <c r="W39" s="97"/>
+      <c r="X39" s="86" t="s">
         <v>179</v>
       </c>
-      <c r="X38" s="97"/>
-      <c r="Y38" s="6"/>
-      <c r="Z38" s="12" t="s">
+      <c r="Y39" s="97"/>
+      <c r="Z39" s="6"/>
+      <c r="AA39" s="12" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A39" s="127"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="97"/>
-      <c r="E39" s="9">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A40" s="124"/>
+      <c r="B40" s="111" t="s">
+        <v>313</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="97"/>
+      <c r="F40" s="9">
         <v>-1</v>
       </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="97"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9">
+      <c r="G40" s="6"/>
+      <c r="H40" s="97"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9">
         <v>-1</v>
       </c>
-      <c r="K39" s="97"/>
-      <c r="L39" s="9">
+      <c r="L40" s="97"/>
+      <c r="M40" s="9">
         <v>-1</v>
       </c>
-      <c r="M39" s="6"/>
-      <c r="N39" s="97"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="97"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="97"/>
-      <c r="T39" s="97"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="97"/>
-      <c r="W39" s="86" t="s">
+      <c r="N40" s="6"/>
+      <c r="O40" s="97"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="97"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="97"/>
+      <c r="U40" s="97"/>
+      <c r="V40" s="6"/>
+      <c r="W40" s="97"/>
+      <c r="X40" s="86" t="s">
         <v>180</v>
       </c>
-      <c r="X39" s="97"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="12" t="s">
+      <c r="Y40" s="97"/>
+      <c r="Z40" s="6"/>
+      <c r="AA40" s="12" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A40" s="125" t="s">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A41" s="134" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="30" t="s">
+      <c r="B41" s="3"/>
+      <c r="C41" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="D41" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="D40" s="99"/>
-      <c r="E40" s="30" t="s">
+      <c r="E41" s="99"/>
+      <c r="F41" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="F40" s="30" t="s">
+      <c r="G41" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="G40" s="99"/>
-      <c r="H40" s="29" t="s">
+      <c r="H41" s="99"/>
+      <c r="I41" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="I40" s="29" t="s">
+      <c r="J41" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="30" t="s">
+      <c r="K41" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="K40" s="99"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="99"/>
-      <c r="O40" s="29" t="s">
+      <c r="L41" s="99"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="30"/>
+      <c r="O41" s="99"/>
+      <c r="P41" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="P40" s="99"/>
-      <c r="Q40" s="29" t="s">
+      <c r="Q41" s="99"/>
+      <c r="R41" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="R40" s="29" t="s">
+      <c r="S41" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="S40" s="99"/>
-      <c r="T40" s="99"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="99"/>
-      <c r="W40" s="29" t="s">
+      <c r="T41" s="99"/>
+      <c r="U41" s="99"/>
+      <c r="V41" s="30"/>
+      <c r="W41" s="99"/>
+      <c r="X41" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="X40" s="99"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="7" t="s">
+      <c r="Y41" s="99"/>
+      <c r="Z41" s="29"/>
+      <c r="AA41" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A41" s="125"/>
-      <c r="B41" s="8" t="s">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A42" s="134"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="D42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="99"/>
-      <c r="E41" s="8" t="s">
+      <c r="E42" s="99"/>
+      <c r="F42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="G42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G41" s="99"/>
-      <c r="H41" s="8" t="s">
+      <c r="H42" s="99"/>
+      <c r="I42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="J42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J41" s="8" t="s">
+      <c r="K42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K41" s="99"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="99"/>
-      <c r="O41" s="8" t="s">
+      <c r="L42" s="99"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="99"/>
+      <c r="P42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="P41" s="99"/>
-      <c r="Q41" s="8" t="s">
+      <c r="Q42" s="99"/>
+      <c r="R42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="R41" s="8" t="s">
+      <c r="S42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="S41" s="99"/>
-      <c r="T41" s="99"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="99"/>
-      <c r="W41" s="8"/>
-      <c r="X41" s="99"/>
-      <c r="Y41" s="8"/>
-      <c r="Z41" s="7" t="s">
+      <c r="T42" s="99"/>
+      <c r="U42" s="99"/>
+      <c r="V42" s="8"/>
+      <c r="W42" s="99"/>
+      <c r="X42" s="8"/>
+      <c r="Y42" s="99"/>
+      <c r="Z42" s="8"/>
+      <c r="AA42" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A42" s="125"/>
-      <c r="B42" s="8" t="s">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A43" s="134"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="D43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="99"/>
-      <c r="E42" s="8" t="s">
+      <c r="E43" s="99"/>
+      <c r="F43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="G43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G42" s="99"/>
-      <c r="H42" s="8" t="s">
+      <c r="H43" s="99"/>
+      <c r="I43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="J43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J42" s="8" t="s">
+      <c r="K43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K42" s="99"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="99"/>
-      <c r="O42" s="8" t="s">
+      <c r="L43" s="99"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="P42" s="99"/>
-      <c r="Q42" s="8" t="s">
+      <c r="Q43" s="99"/>
+      <c r="R43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="R42" s="8" t="s">
+      <c r="S43" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="S42" s="99"/>
-      <c r="T42" s="99"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="99"/>
-      <c r="W42" s="8"/>
-      <c r="X42" s="99"/>
-      <c r="Y42" s="8"/>
-      <c r="Z42" s="7" t="s">
+      <c r="T43" s="99"/>
+      <c r="U43" s="99"/>
+      <c r="V43" s="8"/>
+      <c r="W43" s="99"/>
+      <c r="X43" s="8"/>
+      <c r="Y43" s="99"/>
+      <c r="Z43" s="8"/>
+      <c r="AA43" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A43" s="125" t="s">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A44" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="99"/>
-      <c r="E43" s="5" t="s">
+      <c r="E44" s="99"/>
+      <c r="F44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G43" s="99"/>
-      <c r="H43" s="5" t="s">
+      <c r="H44" s="99"/>
+      <c r="I44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="J44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="5" t="s">
+      <c r="K44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K43" s="99"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="5" t="s">
+      <c r="L44" s="99"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="99"/>
+      <c r="P44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="5" t="s">
+      <c r="Q44" s="99"/>
+      <c r="R44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="R43" s="5" t="s">
+      <c r="S44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="S43" s="99"/>
-      <c r="T43" s="99"/>
-      <c r="U43" s="5"/>
-      <c r="V43" s="99"/>
-      <c r="W43" s="11" t="s">
+      <c r="T44" s="99"/>
+      <c r="U44" s="99"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="99"/>
+      <c r="X44" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="X43" s="99"/>
-      <c r="Y43" s="5"/>
-      <c r="Z43" s="7" t="s">
+      <c r="Y44" s="99"/>
+      <c r="Z44" s="5"/>
+      <c r="AA44" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A44" s="125"/>
-      <c r="B44" s="112" t="s">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A45" s="134"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="112" t="s">
+      <c r="D45" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="D44" s="99"/>
-      <c r="E44" s="112" t="s">
+      <c r="E45" s="99"/>
+      <c r="F45" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F44" s="112" t="s">
+      <c r="G45" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="G44" s="99"/>
-      <c r="H44" s="112" t="s">
+      <c r="H45" s="99"/>
+      <c r="I45" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="I44" s="112" t="s">
+      <c r="J45" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="J44" s="112" t="s">
+      <c r="K45" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="K44" s="99"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="8"/>
-      <c r="N44" s="99"/>
-      <c r="O44" s="112" t="s">
+      <c r="L45" s="99"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="99"/>
+      <c r="P45" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="P44" s="99"/>
-      <c r="Q44" s="112" t="s">
+      <c r="Q45" s="99"/>
+      <c r="R45" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="R44" s="112" t="s">
+      <c r="S45" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="S44" s="99"/>
-      <c r="T44" s="99"/>
-      <c r="U44" s="8"/>
-      <c r="V44" s="99"/>
-      <c r="W44" s="116"/>
-      <c r="X44" s="99"/>
-      <c r="Y44" s="112"/>
-      <c r="Z44" s="7" t="s">
+      <c r="T45" s="99"/>
+      <c r="U45" s="99"/>
+      <c r="V45" s="8"/>
+      <c r="W45" s="99"/>
+      <c r="X45" s="150"/>
+      <c r="Y45" s="99"/>
+      <c r="Z45" s="131"/>
+      <c r="AA45" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A45" s="125"/>
-      <c r="B45" s="112"/>
-      <c r="C45" s="112"/>
-      <c r="D45" s="99"/>
-      <c r="E45" s="112"/>
-      <c r="F45" s="112"/>
-      <c r="G45" s="99"/>
-      <c r="H45" s="112"/>
-      <c r="I45" s="112"/>
-      <c r="J45" s="112"/>
-      <c r="K45" s="99"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="99"/>
-      <c r="O45" s="112"/>
-      <c r="P45" s="99"/>
-      <c r="Q45" s="112"/>
-      <c r="R45" s="112"/>
-      <c r="S45" s="99"/>
-      <c r="T45" s="99"/>
-      <c r="U45" s="8"/>
-      <c r="V45" s="99"/>
-      <c r="W45" s="117"/>
-      <c r="X45" s="99"/>
-      <c r="Y45" s="112"/>
-      <c r="Z45" s="10" t="s">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A46" s="134"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="131"/>
+      <c r="D46" s="131"/>
+      <c r="E46" s="99"/>
+      <c r="F46" s="131"/>
+      <c r="G46" s="131"/>
+      <c r="H46" s="99"/>
+      <c r="I46" s="131"/>
+      <c r="J46" s="131"/>
+      <c r="K46" s="131"/>
+      <c r="L46" s="99"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="99"/>
+      <c r="P46" s="131"/>
+      <c r="Q46" s="99"/>
+      <c r="R46" s="131"/>
+      <c r="S46" s="131"/>
+      <c r="T46" s="99"/>
+      <c r="U46" s="99"/>
+      <c r="V46" s="8"/>
+      <c r="W46" s="99"/>
+      <c r="X46" s="151"/>
+      <c r="Y46" s="99"/>
+      <c r="Z46" s="131"/>
+      <c r="AA46" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A46" s="125"/>
-      <c r="B46" s="112" t="s">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A47" s="134"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="112" t="s">
+      <c r="D47" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="D46" s="99"/>
-      <c r="E46" s="112" t="s">
+      <c r="E47" s="99"/>
+      <c r="F47" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="F46" s="112" t="s">
+      <c r="G47" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="G46" s="99"/>
-      <c r="H46" s="112" t="s">
+      <c r="H47" s="99"/>
+      <c r="I47" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="I46" s="112" t="s">
+      <c r="J47" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="J46" s="112" t="s">
+      <c r="K47" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="K46" s="99"/>
-      <c r="L46" s="8"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="99"/>
-      <c r="O46" s="112" t="s">
+      <c r="L47" s="99"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="99"/>
+      <c r="P47" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="P46" s="99"/>
-      <c r="Q46" s="112" t="s">
+      <c r="Q47" s="99"/>
+      <c r="R47" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="R46" s="112" t="s">
+      <c r="S47" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="S46" s="99"/>
-      <c r="T46" s="99"/>
-      <c r="U46" s="8"/>
-      <c r="V46" s="99"/>
-      <c r="W46" s="116" t="s">
+      <c r="T47" s="99"/>
+      <c r="U47" s="99"/>
+      <c r="V47" s="8"/>
+      <c r="W47" s="99"/>
+      <c r="X47" s="150" t="s">
         <v>230</v>
       </c>
-      <c r="X46" s="99"/>
-      <c r="Y46" s="112"/>
-      <c r="Z46" s="7" t="s">
+      <c r="Y47" s="99"/>
+      <c r="Z47" s="131"/>
+      <c r="AA47" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A47" s="125"/>
-      <c r="B47" s="112"/>
-      <c r="C47" s="112"/>
-      <c r="D47" s="99"/>
-      <c r="E47" s="112"/>
-      <c r="F47" s="112"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="112"/>
-      <c r="I47" s="112"/>
-      <c r="J47" s="112"/>
-      <c r="K47" s="99"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="99"/>
-      <c r="O47" s="112"/>
-      <c r="P47" s="99"/>
-      <c r="Q47" s="112"/>
-      <c r="R47" s="112"/>
-      <c r="S47" s="99"/>
-      <c r="T47" s="99"/>
-      <c r="U47" s="8"/>
-      <c r="V47" s="99"/>
-      <c r="W47" s="117"/>
-      <c r="X47" s="99"/>
-      <c r="Y47" s="112"/>
-      <c r="Z47" s="10" t="s">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A48" s="134"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="131"/>
+      <c r="D48" s="131"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="131"/>
+      <c r="G48" s="131"/>
+      <c r="H48" s="99"/>
+      <c r="I48" s="131"/>
+      <c r="J48" s="131"/>
+      <c r="K48" s="131"/>
+      <c r="L48" s="99"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="99"/>
+      <c r="P48" s="131"/>
+      <c r="Q48" s="99"/>
+      <c r="R48" s="131"/>
+      <c r="S48" s="131"/>
+      <c r="T48" s="99"/>
+      <c r="U48" s="99"/>
+      <c r="V48" s="8"/>
+      <c r="W48" s="99"/>
+      <c r="X48" s="151"/>
+      <c r="Y48" s="99"/>
+      <c r="Z48" s="131"/>
+      <c r="AA48" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A48" s="125"/>
-      <c r="B48" s="112" t="s">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A49" s="134"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="112" t="s">
+      <c r="D49" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="D48" s="99"/>
-      <c r="E48" s="112" t="s">
+      <c r="E49" s="99"/>
+      <c r="F49" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="F48" s="112" t="s">
+      <c r="G49" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="G48" s="99"/>
-      <c r="H48" s="112" t="s">
+      <c r="H49" s="99"/>
+      <c r="I49" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="I48" s="112" t="s">
+      <c r="J49" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="J48" s="112" t="s">
+      <c r="K49" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="K48" s="99"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="99"/>
-      <c r="O48" s="112" t="s">
+      <c r="L49" s="99"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="99"/>
+      <c r="P49" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="P48" s="99"/>
-      <c r="Q48" s="112" t="s">
+      <c r="Q49" s="99"/>
+      <c r="R49" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="R48" s="112" t="s">
+      <c r="S49" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="S48" s="99"/>
-      <c r="T48" s="99"/>
-      <c r="U48" s="8"/>
-      <c r="V48" s="99"/>
-      <c r="W48" s="116" t="s">
+      <c r="T49" s="99"/>
+      <c r="U49" s="99"/>
+      <c r="V49" s="8"/>
+      <c r="W49" s="99"/>
+      <c r="X49" s="150" t="s">
         <v>232</v>
       </c>
-      <c r="X48" s="99"/>
-      <c r="Y48" s="112"/>
-      <c r="Z48" s="7" t="s">
+      <c r="Y49" s="99"/>
+      <c r="Z49" s="131"/>
+      <c r="AA49" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A49" s="125"/>
-      <c r="B49" s="112"/>
-      <c r="C49" s="112"/>
-      <c r="D49" s="99"/>
-      <c r="E49" s="112"/>
-      <c r="F49" s="112"/>
-      <c r="G49" s="99"/>
-      <c r="H49" s="112"/>
-      <c r="I49" s="112"/>
-      <c r="J49" s="112"/>
-      <c r="K49" s="99"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="99"/>
-      <c r="O49" s="112"/>
-      <c r="P49" s="99"/>
-      <c r="Q49" s="112"/>
-      <c r="R49" s="112"/>
-      <c r="S49" s="99"/>
-      <c r="T49" s="99"/>
-      <c r="U49" s="8"/>
-      <c r="V49" s="99"/>
-      <c r="W49" s="117"/>
-      <c r="X49" s="99"/>
-      <c r="Y49" s="112"/>
-      <c r="Z49" s="10" t="s">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A50" s="134"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="131"/>
+      <c r="D50" s="131"/>
+      <c r="E50" s="99"/>
+      <c r="F50" s="131"/>
+      <c r="G50" s="131"/>
+      <c r="H50" s="99"/>
+      <c r="I50" s="131"/>
+      <c r="J50" s="131"/>
+      <c r="K50" s="131"/>
+      <c r="L50" s="99"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="99"/>
+      <c r="P50" s="131"/>
+      <c r="Q50" s="99"/>
+      <c r="R50" s="131"/>
+      <c r="S50" s="131"/>
+      <c r="T50" s="99"/>
+      <c r="U50" s="99"/>
+      <c r="V50" s="8"/>
+      <c r="W50" s="99"/>
+      <c r="X50" s="151"/>
+      <c r="Y50" s="99"/>
+      <c r="Z50" s="131"/>
+      <c r="AA50" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A50" s="125" t="s">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A51" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="99"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="99"/>
-      <c r="H50" s="29" t="s">
+      <c r="B51" s="3"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="99"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="99"/>
+      <c r="I51" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I50" s="29" t="s">
+      <c r="J51" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="J50" s="9"/>
-      <c r="K50" s="99"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="99"/>
-      <c r="O50" s="29" t="s">
+      <c r="K51" s="9"/>
+      <c r="L51" s="99"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+      <c r="O51" s="99"/>
+      <c r="P51" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="P50" s="99"/>
-      <c r="Q50" s="29" t="s">
+      <c r="Q51" s="99"/>
+      <c r="R51" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="R50" s="29" t="s">
+      <c r="S51" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="S50" s="99"/>
-      <c r="T50" s="99"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="99"/>
-      <c r="W50" s="118" t="s">
+      <c r="T51" s="99"/>
+      <c r="U51" s="99"/>
+      <c r="V51" s="9"/>
+      <c r="W51" s="99"/>
+      <c r="X51" s="155" t="s">
         <v>237</v>
       </c>
-      <c r="X50" s="99"/>
-      <c r="Y50" s="29"/>
-      <c r="Z50" s="7" t="s">
+      <c r="Y51" s="99"/>
+      <c r="Z51" s="29"/>
+      <c r="AA51" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A51" s="125"/>
-      <c r="B51" s="8" t="s">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A52" s="134"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="D52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="99"/>
-      <c r="E51" s="8" t="s">
+      <c r="E52" s="99"/>
+      <c r="F52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="G52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G51" s="99"/>
-      <c r="H51" s="8" t="s">
+      <c r="H52" s="99"/>
+      <c r="I52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I51" s="8" t="s">
+      <c r="J52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J51" s="8" t="s">
+      <c r="K52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K51" s="99"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8"/>
-      <c r="N51" s="99"/>
-      <c r="O51" s="8" t="s">
+      <c r="L52" s="99"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="99"/>
+      <c r="P52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="P51" s="99"/>
-      <c r="Q51" s="8" t="s">
+      <c r="Q52" s="99"/>
+      <c r="R52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="R51" s="8" t="s">
+      <c r="S52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="S51" s="99"/>
-      <c r="T51" s="99"/>
-      <c r="U51" s="8"/>
-      <c r="V51" s="99"/>
-      <c r="W51" s="119"/>
-      <c r="X51" s="99"/>
-      <c r="Y51" s="8"/>
-      <c r="Z51" s="7" t="s">
+      <c r="T52" s="99"/>
+      <c r="U52" s="99"/>
+      <c r="V52" s="8"/>
+      <c r="W52" s="99"/>
+      <c r="X52" s="156"/>
+      <c r="Y52" s="99"/>
+      <c r="Z52" s="8"/>
+      <c r="AA52" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A52" s="125" t="s">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A53" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="B52" s="111" t="s">
+      <c r="B53" s="3"/>
+      <c r="C53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="C52" s="111" t="s">
+      <c r="D53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="D52" s="99"/>
-      <c r="E52" s="111" t="s">
+      <c r="E53" s="99"/>
+      <c r="F53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="F52" s="111" t="s">
+      <c r="G53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="G52" s="99"/>
-      <c r="H52" s="111" t="s">
+      <c r="H53" s="99"/>
+      <c r="I53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="I52" s="111" t="s">
+      <c r="J53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="J52" s="111" t="s">
+      <c r="K53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="K52" s="99"/>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="99"/>
-      <c r="O52" s="111" t="s">
+      <c r="L53" s="99"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="99"/>
+      <c r="P53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="P52" s="99"/>
-      <c r="Q52" s="111" t="s">
+      <c r="Q53" s="99"/>
+      <c r="R53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="R52" s="111" t="s">
+      <c r="S53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="S52" s="99"/>
-      <c r="T52" s="99"/>
-      <c r="U52" s="5"/>
-      <c r="V52" s="99"/>
-      <c r="W52" s="111" t="s">
+      <c r="T53" s="99"/>
+      <c r="U53" s="99"/>
+      <c r="V53" s="5"/>
+      <c r="W53" s="99"/>
+      <c r="X53" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="X52" s="99"/>
-      <c r="Y52" s="111"/>
-      <c r="Z52" s="7" t="s">
+      <c r="Y53" s="99"/>
+      <c r="Z53" s="132"/>
+      <c r="AA53" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A53" s="125"/>
-      <c r="B53" s="111"/>
-      <c r="C53" s="111"/>
-      <c r="D53" s="99"/>
-      <c r="E53" s="111"/>
-      <c r="F53" s="111"/>
-      <c r="G53" s="99"/>
-      <c r="H53" s="111"/>
-      <c r="I53" s="111"/>
-      <c r="J53" s="111"/>
-      <c r="K53" s="99"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="99"/>
-      <c r="O53" s="111"/>
-      <c r="P53" s="99"/>
-      <c r="Q53" s="111"/>
-      <c r="R53" s="111"/>
-      <c r="S53" s="99"/>
-      <c r="T53" s="99"/>
-      <c r="U53" s="5"/>
-      <c r="V53" s="99"/>
-      <c r="W53" s="111"/>
-      <c r="X53" s="99"/>
-      <c r="Y53" s="111"/>
-      <c r="Z53" s="10" t="s">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A54" s="134"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="132"/>
+      <c r="D54" s="132"/>
+      <c r="E54" s="99"/>
+      <c r="F54" s="132"/>
+      <c r="G54" s="132"/>
+      <c r="H54" s="99"/>
+      <c r="I54" s="132"/>
+      <c r="J54" s="132"/>
+      <c r="K54" s="132"/>
+      <c r="L54" s="99"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="99"/>
+      <c r="P54" s="132"/>
+      <c r="Q54" s="99"/>
+      <c r="R54" s="132"/>
+      <c r="S54" s="132"/>
+      <c r="T54" s="99"/>
+      <c r="U54" s="99"/>
+      <c r="V54" s="5"/>
+      <c r="W54" s="99"/>
+      <c r="X54" s="132"/>
+      <c r="Y54" s="99"/>
+      <c r="Z54" s="132"/>
+      <c r="AA54" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A54" s="125"/>
-      <c r="B54" s="8" t="s">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A55" s="134"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="D55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D54" s="99"/>
-      <c r="E54" s="8" t="s">
+      <c r="E55" s="99"/>
+      <c r="F55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="99"/>
-      <c r="H54" s="8" t="s">
+      <c r="G55" s="8"/>
+      <c r="H55" s="99"/>
+      <c r="I55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="J55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="K55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K54" s="99"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="8"/>
-      <c r="N54" s="99"/>
-      <c r="O54" s="8" t="s">
+      <c r="L55" s="99"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="99"/>
+      <c r="P55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="P54" s="99"/>
-      <c r="Q54" s="8" t="s">
+      <c r="Q55" s="99"/>
+      <c r="R55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="R54" s="8" t="s">
+      <c r="S55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="S54" s="99"/>
-      <c r="T54" s="99"/>
-      <c r="U54" s="8"/>
-      <c r="V54" s="99"/>
-      <c r="W54" s="8" t="s">
+      <c r="T55" s="99"/>
+      <c r="U55" s="99"/>
+      <c r="V55" s="8"/>
+      <c r="W55" s="99"/>
+      <c r="X55" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="X54" s="99"/>
-      <c r="Y54" s="8"/>
-      <c r="Z54" s="7" t="s">
+      <c r="Y55" s="99"/>
+      <c r="Z55" s="8"/>
+      <c r="AA55" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A55" s="125" t="s">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A56" s="134" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="111" t="s">
+      <c r="B56" s="3"/>
+      <c r="C56" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="111" t="s">
+      <c r="D56" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="99"/>
-      <c r="E55" s="111" t="s">
+      <c r="E56" s="99"/>
+      <c r="F56" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="111" t="s">
+      <c r="G56" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="G55" s="99"/>
-      <c r="H55" s="111" t="s">
+      <c r="H56" s="99"/>
+      <c r="I56" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="I55" s="111" t="s">
+      <c r="J56" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="J55" s="111" t="s">
+      <c r="K56" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="K55" s="99"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="99"/>
-      <c r="O55" s="111" t="s">
+      <c r="L56" s="99"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="99"/>
+      <c r="P56" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="P55" s="99"/>
-      <c r="Q55" s="111" t="s">
+      <c r="Q56" s="99"/>
+      <c r="R56" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="R55" s="111" t="s">
+      <c r="S56" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="S55" s="99"/>
-      <c r="T55" s="99"/>
-      <c r="U55" s="5"/>
-      <c r="V55" s="99"/>
-      <c r="W55" s="111" t="s">
+      <c r="T56" s="99"/>
+      <c r="U56" s="99"/>
+      <c r="V56" s="5"/>
+      <c r="W56" s="99"/>
+      <c r="X56" s="132" t="s">
         <v>233</v>
       </c>
-      <c r="X55" s="99"/>
-      <c r="Y55" s="111"/>
-      <c r="Z55" s="7" t="s">
+      <c r="Y56" s="99"/>
+      <c r="Z56" s="132"/>
+      <c r="AA56" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A56" s="125"/>
-      <c r="B56" s="111"/>
-      <c r="C56" s="111"/>
-      <c r="D56" s="99"/>
-      <c r="E56" s="111"/>
-      <c r="F56" s="111"/>
-      <c r="G56" s="99"/>
-      <c r="H56" s="111"/>
-      <c r="I56" s="111"/>
-      <c r="J56" s="111"/>
-      <c r="K56" s="99"/>
-      <c r="L56" s="5"/>
-      <c r="M56" s="5"/>
-      <c r="N56" s="99"/>
-      <c r="O56" s="111"/>
-      <c r="P56" s="99"/>
-      <c r="Q56" s="111"/>
-      <c r="R56" s="111"/>
-      <c r="S56" s="99"/>
-      <c r="T56" s="99"/>
-      <c r="U56" s="5"/>
-      <c r="V56" s="99"/>
-      <c r="W56" s="111"/>
-      <c r="X56" s="99"/>
-      <c r="Y56" s="111"/>
-      <c r="Z56" s="10" t="s">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A57" s="134"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="132"/>
+      <c r="D57" s="132"/>
+      <c r="E57" s="99"/>
+      <c r="F57" s="132"/>
+      <c r="G57" s="132"/>
+      <c r="H57" s="99"/>
+      <c r="I57" s="132"/>
+      <c r="J57" s="132"/>
+      <c r="K57" s="132"/>
+      <c r="L57" s="99"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="99"/>
+      <c r="P57" s="132"/>
+      <c r="Q57" s="99"/>
+      <c r="R57" s="132"/>
+      <c r="S57" s="132"/>
+      <c r="T57" s="99"/>
+      <c r="U57" s="99"/>
+      <c r="V57" s="5"/>
+      <c r="W57" s="99"/>
+      <c r="X57" s="132"/>
+      <c r="Y57" s="99"/>
+      <c r="Z57" s="132"/>
+      <c r="AA57" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A57" s="125"/>
-      <c r="B57" s="112" t="s">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A58" s="134"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="112" t="s">
+      <c r="D58" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="D57" s="99"/>
-      <c r="E57" s="112" t="s">
+      <c r="E58" s="99"/>
+      <c r="F58" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="F57" s="112" t="s">
+      <c r="G58" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="G57" s="99"/>
-      <c r="H57" s="112" t="s">
+      <c r="H58" s="99"/>
+      <c r="I58" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="I57" s="112" t="s">
+      <c r="J58" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="J57" s="112" t="s">
+      <c r="K58" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="K57" s="99"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
-      <c r="N57" s="99"/>
-      <c r="O57" s="112" t="s">
+      <c r="L58" s="99"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="8"/>
+      <c r="O58" s="99"/>
+      <c r="P58" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="P57" s="99"/>
-      <c r="Q57" s="112" t="s">
+      <c r="Q58" s="99"/>
+      <c r="R58" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="R57" s="112" t="s">
+      <c r="S58" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="S57" s="99"/>
-      <c r="T57" s="99"/>
-      <c r="U57" s="8"/>
-      <c r="V57" s="99"/>
-      <c r="W57" s="112" t="s">
+      <c r="T58" s="99"/>
+      <c r="U58" s="99"/>
+      <c r="V58" s="8"/>
+      <c r="W58" s="99"/>
+      <c r="X58" s="131" t="s">
         <v>234</v>
       </c>
-      <c r="X57" s="99"/>
-      <c r="Y57" s="112"/>
-      <c r="Z57" s="7" t="s">
+      <c r="Y58" s="99"/>
+      <c r="Z58" s="131"/>
+      <c r="AA58" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A58" s="125"/>
-      <c r="B58" s="112"/>
-      <c r="C58" s="112"/>
-      <c r="D58" s="99"/>
-      <c r="E58" s="112"/>
-      <c r="F58" s="112"/>
-      <c r="G58" s="99"/>
-      <c r="H58" s="112"/>
-      <c r="I58" s="112"/>
-      <c r="J58" s="112"/>
-      <c r="K58" s="99"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
-      <c r="N58" s="99"/>
-      <c r="O58" s="112"/>
-      <c r="P58" s="99"/>
-      <c r="Q58" s="112"/>
-      <c r="R58" s="112"/>
-      <c r="S58" s="99"/>
-      <c r="T58" s="99"/>
-      <c r="U58" s="8"/>
-      <c r="V58" s="99"/>
-      <c r="W58" s="112"/>
-      <c r="X58" s="99"/>
-      <c r="Y58" s="112"/>
-      <c r="Z58" s="10" t="s">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A59" s="134"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="131"/>
+      <c r="D59" s="131"/>
+      <c r="E59" s="99"/>
+      <c r="F59" s="131"/>
+      <c r="G59" s="131"/>
+      <c r="H59" s="99"/>
+      <c r="I59" s="131"/>
+      <c r="J59" s="131"/>
+      <c r="K59" s="131"/>
+      <c r="L59" s="99"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="8"/>
+      <c r="O59" s="99"/>
+      <c r="P59" s="131"/>
+      <c r="Q59" s="99"/>
+      <c r="R59" s="131"/>
+      <c r="S59" s="131"/>
+      <c r="T59" s="99"/>
+      <c r="U59" s="99"/>
+      <c r="V59" s="8"/>
+      <c r="W59" s="99"/>
+      <c r="X59" s="131"/>
+      <c r="Y59" s="99"/>
+      <c r="Z59" s="131"/>
+      <c r="AA59" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A59" s="3" t="s">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A60" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B60" s="3"/>
+      <c r="C60" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="D60" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D59" s="99"/>
-      <c r="E59" s="14" t="s">
+      <c r="E60" s="99"/>
+      <c r="F60" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="G60" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G59" s="99"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="14" t="s">
+      <c r="H60" s="99"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
+      <c r="K60" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K59" s="99"/>
-      <c r="L59" s="14"/>
-      <c r="M59" s="14"/>
-      <c r="N59" s="99"/>
-      <c r="O59" s="9"/>
-      <c r="P59" s="99"/>
-      <c r="Q59" s="9"/>
-      <c r="R59" s="9"/>
-      <c r="S59" s="99"/>
-      <c r="T59" s="99"/>
-      <c r="U59" s="14"/>
-      <c r="V59" s="99"/>
-      <c r="W59" s="9"/>
-      <c r="X59" s="99"/>
-      <c r="Y59" s="9"/>
-      <c r="Z59" s="7" t="s">
+      <c r="L60" s="99"/>
+      <c r="M60" s="14"/>
+      <c r="N60" s="14"/>
+      <c r="O60" s="99"/>
+      <c r="P60" s="9"/>
+      <c r="Q60" s="99"/>
+      <c r="R60" s="9"/>
+      <c r="S60" s="9"/>
+      <c r="T60" s="99"/>
+      <c r="U60" s="99"/>
+      <c r="V60" s="14"/>
+      <c r="W60" s="99"/>
+      <c r="X60" s="9"/>
+      <c r="Y60" s="99"/>
+      <c r="Z60" s="9"/>
+      <c r="AA60" s="7" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A60" s="3" t="s">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A61" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="99"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="99"/>
-      <c r="H60" s="29" t="s">
+      <c r="B61" s="3"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="99"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="99"/>
+      <c r="I61" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="I60" s="29" t="s">
+      <c r="J61" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="J60" s="9"/>
-      <c r="K60" s="99"/>
-      <c r="L60" s="9"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="99"/>
-      <c r="O60" s="29" t="s">
+      <c r="K61" s="9"/>
+      <c r="L61" s="99"/>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9"/>
+      <c r="O61" s="99"/>
+      <c r="P61" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="P60" s="99"/>
-      <c r="Q60" s="29" t="s">
+      <c r="Q61" s="99"/>
+      <c r="R61" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="R60" s="29" t="s">
+      <c r="S61" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="S60" s="99"/>
-      <c r="T60" s="99"/>
-      <c r="U60" s="9"/>
-      <c r="V60" s="99"/>
-      <c r="W60" s="29" t="s">
+      <c r="T61" s="99"/>
+      <c r="U61" s="99"/>
+      <c r="V61" s="9"/>
+      <c r="W61" s="99"/>
+      <c r="X61" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="X60" s="99"/>
-      <c r="Y60" s="29"/>
-      <c r="Z60" s="7" t="s">
+      <c r="Y61" s="99"/>
+      <c r="Z61" s="29"/>
+      <c r="AA61" s="7" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A61" s="141" t="s">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A62" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="99"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="99"/>
-      <c r="H61" s="122" t="s">
+      <c r="B62" s="116"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="99"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="99"/>
+      <c r="I62" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="I61" s="122" t="s">
+      <c r="J62" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="J61" s="9"/>
-      <c r="K61" s="99"/>
-      <c r="L61" s="9"/>
-      <c r="M61" s="9"/>
-      <c r="N61" s="99"/>
-      <c r="O61" s="122" t="s">
+      <c r="K62" s="9"/>
+      <c r="L62" s="99"/>
+      <c r="M62" s="9"/>
+      <c r="N62" s="9"/>
+      <c r="O62" s="99"/>
+      <c r="P62" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="P61" s="99"/>
-      <c r="Q61" s="122" t="s">
+      <c r="Q62" s="99"/>
+      <c r="R62" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="R61" s="122" t="s">
+      <c r="S62" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="S61" s="99"/>
-      <c r="T61" s="99"/>
-      <c r="U61" s="9"/>
-      <c r="V61" s="99"/>
-      <c r="W61" s="9"/>
-      <c r="X61" s="99"/>
-      <c r="Y61" s="122"/>
-      <c r="Z61" s="7" t="s">
+      <c r="T62" s="99"/>
+      <c r="U62" s="99"/>
+      <c r="V62" s="9"/>
+      <c r="W62" s="99"/>
+      <c r="X62" s="9"/>
+      <c r="Y62" s="99"/>
+      <c r="Z62" s="140"/>
+      <c r="AA62" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A62" s="145"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="99"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="99"/>
-      <c r="H62" s="122"/>
-      <c r="I62" s="122"/>
-      <c r="J62" s="9"/>
-      <c r="K62" s="99"/>
-      <c r="L62" s="9"/>
-      <c r="M62" s="9"/>
-      <c r="N62" s="99"/>
-      <c r="O62" s="122"/>
-      <c r="P62" s="99"/>
-      <c r="Q62" s="122"/>
-      <c r="R62" s="122"/>
-      <c r="S62" s="99"/>
-      <c r="T62" s="99"/>
-      <c r="U62" s="9"/>
-      <c r="V62" s="99"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="99"/>
-      <c r="Y62" s="122"/>
-      <c r="Z62" s="10" t="s">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A63" s="139"/>
+      <c r="B63" s="117"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="99"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="99"/>
+      <c r="I63" s="140"/>
+      <c r="J63" s="140"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="99"/>
+      <c r="M63" s="9"/>
+      <c r="N63" s="9"/>
+      <c r="O63" s="99"/>
+      <c r="P63" s="140"/>
+      <c r="Q63" s="99"/>
+      <c r="R63" s="140"/>
+      <c r="S63" s="140"/>
+      <c r="T63" s="99"/>
+      <c r="U63" s="99"/>
+      <c r="V63" s="9"/>
+      <c r="W63" s="99"/>
+      <c r="X63" s="9"/>
+      <c r="Y63" s="99"/>
+      <c r="Z63" s="140"/>
+      <c r="AA63" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A63" s="145"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="99"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="99"/>
-      <c r="H63" s="122"/>
-      <c r="I63" s="122"/>
-      <c r="J63" s="9"/>
-      <c r="K63" s="99"/>
-      <c r="L63" s="9"/>
-      <c r="M63" s="9"/>
-      <c r="N63" s="99"/>
-      <c r="O63" s="122"/>
-      <c r="P63" s="99"/>
-      <c r="Q63" s="122"/>
-      <c r="R63" s="122"/>
-      <c r="S63" s="99"/>
-      <c r="T63" s="99"/>
-      <c r="U63" s="9"/>
-      <c r="V63" s="99"/>
-      <c r="W63" s="9"/>
-      <c r="X63" s="99"/>
-      <c r="Y63" s="122"/>
-      <c r="Z63" s="15" t="s">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A64" s="139"/>
+      <c r="B64" s="117"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="99"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="99"/>
+      <c r="I64" s="140"/>
+      <c r="J64" s="140"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="99"/>
+      <c r="M64" s="9"/>
+      <c r="N64" s="9"/>
+      <c r="O64" s="99"/>
+      <c r="P64" s="140"/>
+      <c r="Q64" s="99"/>
+      <c r="R64" s="140"/>
+      <c r="S64" s="140"/>
+      <c r="T64" s="99"/>
+      <c r="U64" s="99"/>
+      <c r="V64" s="9"/>
+      <c r="W64" s="99"/>
+      <c r="X64" s="9"/>
+      <c r="Y64" s="99"/>
+      <c r="Z64" s="140"/>
+      <c r="AA64" s="15" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A64" s="145"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="99"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="99"/>
-      <c r="H64" s="122" t="s">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A65" s="139"/>
+      <c r="B65" s="117"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="99"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="99"/>
+      <c r="I65" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="I64" s="122" t="s">
+      <c r="J65" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="J64" s="9"/>
-      <c r="K64" s="99"/>
-      <c r="L64" s="9"/>
-      <c r="M64" s="9"/>
-      <c r="N64" s="99"/>
-      <c r="O64" s="122" t="s">
+      <c r="K65" s="9"/>
+      <c r="L65" s="99"/>
+      <c r="M65" s="9"/>
+      <c r="N65" s="9"/>
+      <c r="O65" s="99"/>
+      <c r="P65" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="P64" s="99"/>
-      <c r="Q64" s="122" t="s">
+      <c r="Q65" s="99"/>
+      <c r="R65" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="R64" s="122" t="s">
+      <c r="S65" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="S64" s="99"/>
-      <c r="T64" s="99"/>
-      <c r="U64" s="9"/>
-      <c r="V64" s="99"/>
-      <c r="W64" s="9"/>
-      <c r="X64" s="99"/>
-      <c r="Y64" s="122"/>
-      <c r="Z64" s="7" t="s">
+      <c r="T65" s="99"/>
+      <c r="U65" s="99"/>
+      <c r="V65" s="9"/>
+      <c r="W65" s="99"/>
+      <c r="X65" s="9"/>
+      <c r="Y65" s="99"/>
+      <c r="Z65" s="140"/>
+      <c r="AA65" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A65" s="145"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="99"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="99"/>
-      <c r="H65" s="122"/>
-      <c r="I65" s="122"/>
-      <c r="J65" s="9"/>
-      <c r="K65" s="99"/>
-      <c r="L65" s="9"/>
-      <c r="M65" s="9"/>
-      <c r="N65" s="99"/>
-      <c r="O65" s="122"/>
-      <c r="P65" s="99"/>
-      <c r="Q65" s="122"/>
-      <c r="R65" s="122"/>
-      <c r="S65" s="99"/>
-      <c r="T65" s="99"/>
-      <c r="U65" s="9"/>
-      <c r="V65" s="99"/>
-      <c r="W65" s="9"/>
-      <c r="X65" s="99"/>
-      <c r="Y65" s="122"/>
-      <c r="Z65" s="10" t="s">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A66" s="139"/>
+      <c r="B66" s="117"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="99"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="99"/>
+      <c r="I66" s="140"/>
+      <c r="J66" s="140"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="99"/>
+      <c r="M66" s="9"/>
+      <c r="N66" s="9"/>
+      <c r="O66" s="99"/>
+      <c r="P66" s="140"/>
+      <c r="Q66" s="99"/>
+      <c r="R66" s="140"/>
+      <c r="S66" s="140"/>
+      <c r="T66" s="99"/>
+      <c r="U66" s="99"/>
+      <c r="V66" s="9"/>
+      <c r="W66" s="99"/>
+      <c r="X66" s="9"/>
+      <c r="Y66" s="99"/>
+      <c r="Z66" s="140"/>
+      <c r="AA66" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A66" s="145"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="99"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="99"/>
-      <c r="H66" s="122"/>
-      <c r="I66" s="122"/>
-      <c r="J66" s="9"/>
-      <c r="K66" s="99"/>
-      <c r="L66" s="9"/>
-      <c r="M66" s="9"/>
-      <c r="N66" s="99"/>
-      <c r="O66" s="122"/>
-      <c r="P66" s="99"/>
-      <c r="Q66" s="122"/>
-      <c r="R66" s="122"/>
-      <c r="S66" s="99"/>
-      <c r="T66" s="99"/>
-      <c r="U66" s="9"/>
-      <c r="V66" s="99"/>
-      <c r="W66" s="9"/>
-      <c r="X66" s="99"/>
-      <c r="Y66" s="122"/>
-      <c r="Z66" s="15" t="s">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A67" s="139"/>
+      <c r="B67" s="117"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="99"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="99"/>
+      <c r="I67" s="140"/>
+      <c r="J67" s="140"/>
+      <c r="K67" s="9"/>
+      <c r="L67" s="99"/>
+      <c r="M67" s="9"/>
+      <c r="N67" s="9"/>
+      <c r="O67" s="99"/>
+      <c r="P67" s="140"/>
+      <c r="Q67" s="99"/>
+      <c r="R67" s="140"/>
+      <c r="S67" s="140"/>
+      <c r="T67" s="99"/>
+      <c r="U67" s="99"/>
+      <c r="V67" s="9"/>
+      <c r="W67" s="99"/>
+      <c r="X67" s="9"/>
+      <c r="Y67" s="99"/>
+      <c r="Z67" s="140"/>
+      <c r="AA67" s="15" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A67" s="145"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="99"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="99"/>
-      <c r="H67" s="122" t="s">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A68" s="139"/>
+      <c r="B68" s="117"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="99"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="99"/>
+      <c r="I68" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="I67" s="122" t="s">
+      <c r="J68" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="J67" s="9"/>
-      <c r="K67" s="99"/>
-      <c r="L67" s="9"/>
-      <c r="M67" s="9"/>
-      <c r="N67" s="99"/>
-      <c r="O67" s="122" t="s">
+      <c r="K68" s="9"/>
+      <c r="L68" s="99"/>
+      <c r="M68" s="9"/>
+      <c r="N68" s="9"/>
+      <c r="O68" s="99"/>
+      <c r="P68" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="P67" s="99"/>
-      <c r="Q67" s="122" t="s">
+      <c r="Q68" s="99"/>
+      <c r="R68" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="R67" s="122" t="s">
+      <c r="S68" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="S67" s="99"/>
-      <c r="T67" s="99"/>
-      <c r="U67" s="9"/>
-      <c r="V67" s="99"/>
-      <c r="W67" s="9"/>
-      <c r="X67" s="99"/>
-      <c r="Y67" s="122"/>
-      <c r="Z67" s="7" t="s">
+      <c r="T68" s="99"/>
+      <c r="U68" s="99"/>
+      <c r="V68" s="9"/>
+      <c r="W68" s="99"/>
+      <c r="X68" s="9"/>
+      <c r="Y68" s="99"/>
+      <c r="Z68" s="140"/>
+      <c r="AA68" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A68" s="145"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="99"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="99"/>
-      <c r="H68" s="122"/>
-      <c r="I68" s="122"/>
-      <c r="J68" s="9"/>
-      <c r="K68" s="99"/>
-      <c r="L68" s="9"/>
-      <c r="M68" s="9"/>
-      <c r="N68" s="99"/>
-      <c r="O68" s="122"/>
-      <c r="P68" s="99"/>
-      <c r="Q68" s="122"/>
-      <c r="R68" s="122"/>
-      <c r="S68" s="99"/>
-      <c r="T68" s="99"/>
-      <c r="U68" s="9"/>
-      <c r="V68" s="99"/>
-      <c r="W68" s="9"/>
-      <c r="X68" s="99"/>
-      <c r="Y68" s="122"/>
-      <c r="Z68" s="10" t="s">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A69" s="139"/>
+      <c r="B69" s="117"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="99"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="99"/>
+      <c r="I69" s="140"/>
+      <c r="J69" s="140"/>
+      <c r="K69" s="9"/>
+      <c r="L69" s="99"/>
+      <c r="M69" s="9"/>
+      <c r="N69" s="9"/>
+      <c r="O69" s="99"/>
+      <c r="P69" s="140"/>
+      <c r="Q69" s="99"/>
+      <c r="R69" s="140"/>
+      <c r="S69" s="140"/>
+      <c r="T69" s="99"/>
+      <c r="U69" s="99"/>
+      <c r="V69" s="9"/>
+      <c r="W69" s="99"/>
+      <c r="X69" s="9"/>
+      <c r="Y69" s="99"/>
+      <c r="Z69" s="140"/>
+      <c r="AA69" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A69" s="145"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="99"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="99"/>
-      <c r="H69" s="122"/>
-      <c r="I69" s="122"/>
-      <c r="J69" s="9"/>
-      <c r="K69" s="99"/>
-      <c r="L69" s="9"/>
-      <c r="M69" s="9"/>
-      <c r="N69" s="99"/>
-      <c r="O69" s="122"/>
-      <c r="P69" s="99"/>
-      <c r="Q69" s="122"/>
-      <c r="R69" s="122"/>
-      <c r="S69" s="99"/>
-      <c r="T69" s="99"/>
-      <c r="U69" s="9"/>
-      <c r="V69" s="99"/>
-      <c r="W69" s="9"/>
-      <c r="X69" s="99"/>
-      <c r="Y69" s="122"/>
-      <c r="Z69" s="15" t="s">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A70" s="139"/>
+      <c r="B70" s="117"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="99"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="9"/>
+      <c r="H70" s="99"/>
+      <c r="I70" s="140"/>
+      <c r="J70" s="140"/>
+      <c r="K70" s="9"/>
+      <c r="L70" s="99"/>
+      <c r="M70" s="9"/>
+      <c r="N70" s="9"/>
+      <c r="O70" s="99"/>
+      <c r="P70" s="140"/>
+      <c r="Q70" s="99"/>
+      <c r="R70" s="140"/>
+      <c r="S70" s="140"/>
+      <c r="T70" s="99"/>
+      <c r="U70" s="99"/>
+      <c r="V70" s="9"/>
+      <c r="W70" s="99"/>
+      <c r="X70" s="9"/>
+      <c r="Y70" s="99"/>
+      <c r="Z70" s="140"/>
+      <c r="AA70" s="15" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A70" s="145"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="102"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="102"/>
-      <c r="H70" s="131" t="s">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A71" s="139"/>
+      <c r="B71" s="117"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="102"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="102"/>
+      <c r="I71" s="141" t="s">
         <v>52</v>
       </c>
-      <c r="I70" s="131" t="s">
+      <c r="J71" s="141" t="s">
         <v>52</v>
       </c>
-      <c r="J70" s="9"/>
-      <c r="K70" s="102"/>
-      <c r="L70" s="9"/>
-      <c r="M70" s="9"/>
-      <c r="N70" s="102"/>
-      <c r="O70" s="123" t="s">
+      <c r="K71" s="9"/>
+      <c r="L71" s="102"/>
+      <c r="M71" s="9"/>
+      <c r="N71" s="9"/>
+      <c r="O71" s="102"/>
+      <c r="P71" s="143" t="s">
         <v>59</v>
       </c>
-      <c r="P70" s="102"/>
-      <c r="Q70" s="123" t="s">
+      <c r="Q71" s="102"/>
+      <c r="R71" s="143" t="s">
         <v>59</v>
       </c>
-      <c r="R70" s="123" t="s">
+      <c r="S71" s="143" t="s">
         <v>59</v>
       </c>
-      <c r="S70" s="102"/>
-      <c r="T70" s="102"/>
-      <c r="U70" s="9"/>
-      <c r="V70" s="102"/>
-      <c r="W70" s="65"/>
-      <c r="X70" s="102"/>
-      <c r="Y70" s="123"/>
-      <c r="Z70" s="7" t="s">
+      <c r="T71" s="102"/>
+      <c r="U71" s="102"/>
+      <c r="V71" s="9"/>
+      <c r="W71" s="102"/>
+      <c r="X71" s="65"/>
+      <c r="Y71" s="102"/>
+      <c r="Z71" s="143"/>
+      <c r="AA71" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="145"/>
-      <c r="B71" s="49"/>
-      <c r="C71" s="49"/>
-      <c r="D71" s="102"/>
-      <c r="E71" s="49"/>
-      <c r="F71" s="49"/>
-      <c r="G71" s="102"/>
-      <c r="H71" s="132"/>
-      <c r="I71" s="132"/>
-      <c r="J71" s="49"/>
-      <c r="K71" s="102"/>
-      <c r="L71" s="49"/>
-      <c r="M71" s="49"/>
-      <c r="N71" s="102"/>
-      <c r="O71" s="124"/>
-      <c r="P71" s="102"/>
-      <c r="Q71" s="124"/>
-      <c r="R71" s="124"/>
-      <c r="S71" s="102"/>
-      <c r="T71" s="102"/>
-      <c r="U71" s="49"/>
-      <c r="V71" s="102"/>
-      <c r="W71" s="66"/>
-      <c r="X71" s="102"/>
-      <c r="Y71" s="124"/>
-      <c r="Z71" s="56" t="s">
+    <row r="72" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="139"/>
+      <c r="B72" s="117"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="49"/>
+      <c r="E72" s="102"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="102"/>
+      <c r="I72" s="142"/>
+      <c r="J72" s="142"/>
+      <c r="K72" s="49"/>
+      <c r="L72" s="102"/>
+      <c r="M72" s="49"/>
+      <c r="N72" s="49"/>
+      <c r="O72" s="102"/>
+      <c r="P72" s="144"/>
+      <c r="Q72" s="102"/>
+      <c r="R72" s="144"/>
+      <c r="S72" s="144"/>
+      <c r="T72" s="102"/>
+      <c r="U72" s="102"/>
+      <c r="V72" s="49"/>
+      <c r="W72" s="102"/>
+      <c r="X72" s="66"/>
+      <c r="Y72" s="102"/>
+      <c r="Z72" s="144"/>
+      <c r="AA72" s="56" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="142" t="s">
+    <row r="73" spans="1:27" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="136" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="43" t="s">
+      <c r="B73" s="159"/>
+      <c r="C73" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="C72" s="43" t="s">
+      <c r="D73" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="D72" s="99"/>
-      <c r="E72" s="43" t="s">
+      <c r="E73" s="99"/>
+      <c r="F73" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="F72" s="43" t="s">
+      <c r="G73" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="G72" s="99"/>
-      <c r="H72" s="43" t="s">
+      <c r="H73" s="99"/>
+      <c r="I73" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="I72" s="43" t="s">
+      <c r="J73" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="J72" s="43" t="s">
+      <c r="K73" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="K72" s="99"/>
-      <c r="L72" s="43"/>
-      <c r="M72" s="43"/>
-      <c r="N72" s="99"/>
-      <c r="O72" s="9"/>
-      <c r="P72" s="99"/>
-      <c r="Q72" s="9"/>
-      <c r="R72" s="9"/>
-      <c r="S72" s="99"/>
-      <c r="T72" s="99"/>
-      <c r="U72" s="108"/>
-      <c r="V72" s="99"/>
-      <c r="W72" s="88" t="s">
+      <c r="L73" s="99"/>
+      <c r="M73" s="43"/>
+      <c r="N73" s="43"/>
+      <c r="O73" s="99"/>
+      <c r="P73" s="9"/>
+      <c r="Q73" s="99"/>
+      <c r="R73" s="9"/>
+      <c r="S73" s="9"/>
+      <c r="T73" s="99"/>
+      <c r="U73" s="99"/>
+      <c r="V73" s="108"/>
+      <c r="W73" s="99"/>
+      <c r="X73" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="X72" s="99"/>
-      <c r="Y72" s="9"/>
-      <c r="Z72" s="59" t="s">
+      <c r="Y73" s="99"/>
+      <c r="Z73" s="9"/>
+      <c r="AA73" s="59" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A73" s="143"/>
-      <c r="B73" s="62" t="s">
+    <row r="74" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="137"/>
+      <c r="B74" s="160"/>
+      <c r="C74" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="C73" s="63" t="s">
+      <c r="D74" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="D73" s="97"/>
-      <c r="E73" s="64" t="s">
+      <c r="E74" s="97"/>
+      <c r="F74" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="F73" s="64" t="s">
+      <c r="G74" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="G73" s="97"/>
-      <c r="H73" s="70" t="s">
+      <c r="H74" s="97"/>
+      <c r="I74" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="I73" s="70" t="s">
+      <c r="J74" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="J73" s="64" t="s">
+      <c r="K74" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="K73" s="97"/>
-      <c r="L73" s="64" t="s">
+      <c r="L74" s="97"/>
+      <c r="M74" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="M73" s="64" t="s">
+      <c r="N74" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="N73" s="97"/>
-      <c r="O73" s="70" t="s">
+      <c r="O74" s="97"/>
+      <c r="P74" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="P73" s="97"/>
-      <c r="Q73" s="70" t="s">
+      <c r="Q74" s="97"/>
+      <c r="R74" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="R73" s="70" t="s">
+      <c r="S74" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="S73" s="97"/>
-      <c r="T73" s="97"/>
-      <c r="U73" s="64"/>
-      <c r="V73" s="97"/>
-      <c r="W73" s="87" t="s">
+      <c r="T74" s="97"/>
+      <c r="U74" s="97"/>
+      <c r="V74" s="64"/>
+      <c r="W74" s="97"/>
+      <c r="X74" s="87" t="s">
         <v>236</v>
       </c>
-      <c r="X73" s="97"/>
-      <c r="Y73" s="70"/>
-      <c r="Z73" s="60" t="s">
+      <c r="Y74" s="97"/>
+      <c r="Z74" s="70"/>
+      <c r="AA74" s="60" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="74" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A74" s="143"/>
-      <c r="B74" s="67" t="s">
+    <row r="75" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="137"/>
+      <c r="B75" s="160"/>
+      <c r="C75" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="C74" s="68" t="s">
+      <c r="D75" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D74" s="97"/>
-      <c r="E74" s="68" t="s">
+      <c r="E75" s="97"/>
+      <c r="F75" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="F74" s="68" t="s">
+      <c r="G75" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="G74" s="97"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="68" t="s">
+      <c r="H75" s="97"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="9"/>
+      <c r="K75" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="K74" s="97"/>
-      <c r="L74" s="68" t="s">
+      <c r="L75" s="97"/>
+      <c r="M75" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="M74" s="68" t="s">
+      <c r="N75" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="N74" s="97"/>
-      <c r="O74" s="31" t="s">
+      <c r="O75" s="97"/>
+      <c r="P75" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="P74" s="97"/>
-      <c r="Q74" s="31" t="s">
+      <c r="Q75" s="97"/>
+      <c r="R75" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="R74" s="31" t="s">
+      <c r="S75" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="S74" s="97"/>
-      <c r="T74" s="97"/>
-      <c r="U74" s="68"/>
-      <c r="V74" s="97"/>
-      <c r="W74" s="87" t="s">
+      <c r="T75" s="97"/>
+      <c r="U75" s="97"/>
+      <c r="V75" s="68"/>
+      <c r="W75" s="97"/>
+      <c r="X75" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="X74" s="97"/>
-      <c r="Y74" s="31"/>
-      <c r="Z74" s="60" t="s">
+      <c r="Y75" s="97"/>
+      <c r="Z75" s="31"/>
+      <c r="AA75" s="60" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="75" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A75" s="144"/>
-      <c r="B75" s="47" t="s">
+    <row r="76" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="138"/>
+      <c r="B76" s="161"/>
+      <c r="C76" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="C75" s="47" t="s">
+      <c r="D76" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="D75" s="99"/>
-      <c r="E75" s="47" t="s">
+      <c r="E76" s="99"/>
+      <c r="F76" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="F75" s="47" t="s">
+      <c r="G76" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="G75" s="99"/>
-      <c r="H75" s="47" t="s">
+      <c r="H76" s="99"/>
+      <c r="I76" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="I75" s="47" t="s">
+      <c r="J76" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="J75" s="47" t="s">
+      <c r="K76" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="K75" s="99"/>
-      <c r="L75" s="47"/>
-      <c r="M75" s="47"/>
-      <c r="N75" s="99"/>
-      <c r="O75" s="9"/>
-      <c r="P75" s="99"/>
-      <c r="Q75" s="9"/>
-      <c r="R75" s="9"/>
-      <c r="S75" s="99"/>
-      <c r="T75" s="99"/>
-      <c r="U75" s="109"/>
-      <c r="V75" s="99"/>
-      <c r="W75" s="87" t="s">
+      <c r="L76" s="99"/>
+      <c r="M76" s="47"/>
+      <c r="N76" s="47"/>
+      <c r="O76" s="99"/>
+      <c r="P76" s="9"/>
+      <c r="Q76" s="99"/>
+      <c r="R76" s="9"/>
+      <c r="S76" s="9"/>
+      <c r="T76" s="99"/>
+      <c r="U76" s="99"/>
+      <c r="V76" s="109"/>
+      <c r="W76" s="99"/>
+      <c r="X76" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="X75" s="99"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="61"/>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A76" s="140" t="s">
+      <c r="Y76" s="99"/>
+      <c r="Z76" s="9"/>
+      <c r="AA76" s="61"/>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A77" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="B76" s="64" t="s">
+      <c r="B77" s="115"/>
+      <c r="C77" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="C76" s="64" t="s">
+      <c r="D77" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="D76" s="97"/>
-      <c r="E76" s="64" t="s">
+      <c r="E77" s="97"/>
+      <c r="F77" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="F76" s="64" t="s">
+      <c r="G77" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="G76" s="97"/>
-      <c r="H76" s="57"/>
-      <c r="I76" s="57"/>
-      <c r="J76" s="64" t="s">
+      <c r="H77" s="97"/>
+      <c r="I77" s="57"/>
+      <c r="J77" s="57"/>
+      <c r="K77" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="K76" s="97"/>
-      <c r="L76" s="94"/>
-      <c r="M76" s="94"/>
-      <c r="N76" s="97"/>
-      <c r="O76" s="52"/>
-      <c r="P76" s="97"/>
-      <c r="Q76" s="52"/>
-      <c r="R76" s="52"/>
-      <c r="S76" s="97"/>
-      <c r="T76" s="97"/>
-      <c r="U76" s="94"/>
-      <c r="V76" s="97"/>
-      <c r="W76" s="52"/>
-      <c r="X76" s="97"/>
-      <c r="Y76" s="52"/>
-      <c r="Z76" s="58"/>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A77" s="125"/>
-      <c r="B77" s="67" t="s">
+      <c r="L77" s="97"/>
+      <c r="M77" s="94"/>
+      <c r="N77" s="94"/>
+      <c r="O77" s="97"/>
+      <c r="P77" s="52"/>
+      <c r="Q77" s="97"/>
+      <c r="R77" s="52"/>
+      <c r="S77" s="52"/>
+      <c r="T77" s="97"/>
+      <c r="U77" s="97"/>
+      <c r="V77" s="94"/>
+      <c r="W77" s="97"/>
+      <c r="X77" s="52"/>
+      <c r="Y77" s="97"/>
+      <c r="Z77" s="52"/>
+      <c r="AA77" s="58"/>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A78" s="134"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="C77" s="68" t="s">
+      <c r="D78" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D77" s="97"/>
-      <c r="E77" s="68" t="s">
+      <c r="E78" s="97"/>
+      <c r="F78" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="F77" s="68" t="s">
+      <c r="G78" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="G77" s="97"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="68" t="s">
+      <c r="H78" s="97"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="K77" s="97"/>
-      <c r="L77" s="68"/>
-      <c r="M77" s="68"/>
-      <c r="N77" s="97"/>
-      <c r="O77" s="12"/>
-      <c r="P77" s="97"/>
-      <c r="Q77" s="12"/>
-      <c r="R77" s="12"/>
-      <c r="S77" s="97"/>
-      <c r="T77" s="97"/>
-      <c r="U77" s="68"/>
-      <c r="V77" s="97"/>
-      <c r="W77" s="12"/>
-      <c r="X77" s="97"/>
-      <c r="Y77" s="12"/>
-      <c r="Z77" s="12" t="s">
+      <c r="L78" s="97"/>
+      <c r="M78" s="68"/>
+      <c r="N78" s="68"/>
+      <c r="O78" s="97"/>
+      <c r="P78" s="12"/>
+      <c r="Q78" s="97"/>
+      <c r="R78" s="12"/>
+      <c r="S78" s="12"/>
+      <c r="T78" s="97"/>
+      <c r="U78" s="97"/>
+      <c r="V78" s="68"/>
+      <c r="W78" s="97"/>
+      <c r="X78" s="12"/>
+      <c r="Y78" s="97"/>
+      <c r="Z78" s="12"/>
+      <c r="AA78" s="12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="141"/>
-      <c r="B78" s="69" t="s">
+    <row r="79" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A79" s="135"/>
+      <c r="B79" s="116"/>
+      <c r="C79" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C78" s="69" t="s">
+      <c r="D79" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="D78" s="97"/>
-      <c r="E78" s="69" t="s">
+      <c r="E79" s="97"/>
+      <c r="F79" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="F78" s="69" t="s">
+      <c r="G79" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="G78" s="97"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49"/>
-      <c r="J78" s="69" t="s">
+      <c r="H79" s="97"/>
+      <c r="I79" s="49"/>
+      <c r="J79" s="49"/>
+      <c r="K79" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="K78" s="97"/>
-      <c r="L78" s="69"/>
-      <c r="M78" s="69"/>
-      <c r="N78" s="97"/>
-      <c r="O78" s="40"/>
-      <c r="P78" s="97"/>
-      <c r="Q78" s="40"/>
-      <c r="R78" s="40"/>
-      <c r="S78" s="97"/>
-      <c r="T78" s="97"/>
-      <c r="U78" s="69"/>
-      <c r="V78" s="97"/>
-      <c r="W78" s="40"/>
-      <c r="X78" s="97"/>
-      <c r="Y78" s="40"/>
-      <c r="Z78" s="40" t="s">
+      <c r="L79" s="97"/>
+      <c r="M79" s="69"/>
+      <c r="N79" s="69"/>
+      <c r="O79" s="97"/>
+      <c r="P79" s="40"/>
+      <c r="Q79" s="97"/>
+      <c r="R79" s="40"/>
+      <c r="S79" s="40"/>
+      <c r="T79" s="97"/>
+      <c r="U79" s="97"/>
+      <c r="V79" s="69"/>
+      <c r="W79" s="97"/>
+      <c r="X79" s="40"/>
+      <c r="Y79" s="97"/>
+      <c r="Z79" s="40"/>
+      <c r="AA79" s="40" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A79" s="134" t="s">
+    <row r="80" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="125" t="s">
         <v>177</v>
       </c>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="97"/>
-      <c r="E79" s="54" t="s">
+      <c r="B80" s="162"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="97"/>
+      <c r="F80" s="54" t="s">
         <v>180</v>
       </c>
-      <c r="F79" s="54" t="s">
+      <c r="G80" s="54" t="s">
         <v>180</v>
       </c>
-      <c r="G79" s="97"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
-      <c r="J79" s="54"/>
-      <c r="K79" s="97"/>
-      <c r="L79" s="54"/>
-      <c r="M79" s="54"/>
-      <c r="N79" s="97"/>
-      <c r="O79" s="54"/>
-      <c r="P79" s="97"/>
-      <c r="Q79" s="54"/>
-      <c r="R79" s="54"/>
-      <c r="S79" s="97"/>
-      <c r="T79" s="97"/>
-      <c r="U79" s="54"/>
-      <c r="V79" s="97"/>
-      <c r="W79" s="54"/>
-      <c r="X79" s="97"/>
-      <c r="Y79" s="54"/>
-      <c r="Z79" s="44" t="s">
+      <c r="H80" s="97"/>
+      <c r="I80" s="53"/>
+      <c r="J80" s="53"/>
+      <c r="K80" s="54"/>
+      <c r="L80" s="97"/>
+      <c r="M80" s="54"/>
+      <c r="N80" s="54"/>
+      <c r="O80" s="97"/>
+      <c r="P80" s="54"/>
+      <c r="Q80" s="97"/>
+      <c r="R80" s="54"/>
+      <c r="S80" s="54"/>
+      <c r="T80" s="97"/>
+      <c r="U80" s="97"/>
+      <c r="V80" s="54"/>
+      <c r="W80" s="97"/>
+      <c r="X80" s="54"/>
+      <c r="Y80" s="97"/>
+      <c r="Z80" s="54"/>
+      <c r="AA80" s="44" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="80" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A80" s="135"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="97"/>
-      <c r="E80" s="12" t="s">
+    <row r="81" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="126"/>
+      <c r="B81" s="163"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="97"/>
+      <c r="F81" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="F80" s="12" t="s">
+      <c r="G81" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="G80" s="97"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="9"/>
-      <c r="J80" s="12"/>
-      <c r="K80" s="97"/>
-      <c r="L80" s="12"/>
-      <c r="M80" s="12"/>
-      <c r="N80" s="97"/>
-      <c r="O80" s="12"/>
-      <c r="P80" s="97"/>
-      <c r="Q80" s="12"/>
-      <c r="R80" s="12"/>
-      <c r="S80" s="97"/>
-      <c r="T80" s="97"/>
-      <c r="U80" s="12"/>
-      <c r="V80" s="97"/>
-      <c r="W80" s="12"/>
-      <c r="X80" s="97"/>
-      <c r="Y80" s="12"/>
-      <c r="Z80" s="44" t="s">
+      <c r="H81" s="97"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="12"/>
+      <c r="L81" s="97"/>
+      <c r="M81" s="12"/>
+      <c r="N81" s="12"/>
+      <c r="O81" s="97"/>
+      <c r="P81" s="12"/>
+      <c r="Q81" s="97"/>
+      <c r="R81" s="12"/>
+      <c r="S81" s="12"/>
+      <c r="T81" s="97"/>
+      <c r="U81" s="97"/>
+      <c r="V81" s="12"/>
+      <c r="W81" s="97"/>
+      <c r="X81" s="12"/>
+      <c r="Y81" s="97"/>
+      <c r="Z81" s="12"/>
+      <c r="AA81" s="44" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A81" s="135"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="97"/>
-      <c r="E81" s="12" t="s">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A82" s="126"/>
+      <c r="B82" s="163"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="97"/>
+      <c r="F82" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="F81" s="12" t="s">
+      <c r="G82" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="G81" s="97"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="12"/>
-      <c r="K81" s="97"/>
-      <c r="L81" s="12"/>
-      <c r="M81" s="12"/>
-      <c r="N81" s="97"/>
-      <c r="O81" s="12"/>
-      <c r="P81" s="97"/>
-      <c r="Q81" s="12"/>
-      <c r="R81" s="12"/>
-      <c r="S81" s="97"/>
-      <c r="T81" s="97"/>
-      <c r="U81" s="12"/>
-      <c r="V81" s="97"/>
-      <c r="W81" s="12"/>
-      <c r="X81" s="97"/>
-      <c r="Y81" s="12"/>
-      <c r="Z81" s="44" t="s">
+      <c r="H82" s="97"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
+      <c r="K82" s="12"/>
+      <c r="L82" s="97"/>
+      <c r="M82" s="12"/>
+      <c r="N82" s="12"/>
+      <c r="O82" s="97"/>
+      <c r="P82" s="12"/>
+      <c r="Q82" s="97"/>
+      <c r="R82" s="12"/>
+      <c r="S82" s="12"/>
+      <c r="T82" s="97"/>
+      <c r="U82" s="97"/>
+      <c r="V82" s="12"/>
+      <c r="W82" s="97"/>
+      <c r="X82" s="12"/>
+      <c r="Y82" s="97"/>
+      <c r="Z82" s="12"/>
+      <c r="AA82" s="44" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="82" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A82" s="136"/>
-      <c r="B82" s="55"/>
-      <c r="C82" s="55"/>
-      <c r="D82" s="97"/>
-      <c r="E82" s="46" t="s">
+    <row r="83" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="127"/>
+      <c r="B83" s="164"/>
+      <c r="C83" s="55"/>
+      <c r="D83" s="55"/>
+      <c r="E83" s="97"/>
+      <c r="F83" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="F82" s="46" t="s">
+      <c r="G83" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="G82" s="97"/>
-      <c r="H82" s="55"/>
-      <c r="I82" s="55"/>
-      <c r="J82" s="46"/>
-      <c r="K82" s="97"/>
-      <c r="L82" s="46"/>
-      <c r="M82" s="46"/>
-      <c r="N82" s="97"/>
-      <c r="O82" s="46"/>
-      <c r="P82" s="97"/>
-      <c r="Q82" s="46"/>
-      <c r="R82" s="46"/>
-      <c r="S82" s="97"/>
-      <c r="T82" s="97"/>
-      <c r="U82" s="46"/>
-      <c r="V82" s="97"/>
-      <c r="W82" s="46"/>
-      <c r="X82" s="97"/>
-      <c r="Y82" s="46"/>
-      <c r="Z82" s="48" t="s">
+      <c r="H83" s="97"/>
+      <c r="I83" s="55"/>
+      <c r="J83" s="55"/>
+      <c r="K83" s="46"/>
+      <c r="L83" s="97"/>
+      <c r="M83" s="46"/>
+      <c r="N83" s="46"/>
+      <c r="O83" s="97"/>
+      <c r="P83" s="46"/>
+      <c r="Q83" s="97"/>
+      <c r="R83" s="46"/>
+      <c r="S83" s="46"/>
+      <c r="T83" s="97"/>
+      <c r="U83" s="97"/>
+      <c r="V83" s="46"/>
+      <c r="W83" s="97"/>
+      <c r="X83" s="46"/>
+      <c r="Y83" s="97"/>
+      <c r="Z83" s="46"/>
+      <c r="AA83" s="48" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A83" s="137" t="s">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A84" s="128" t="s">
         <v>182</v>
       </c>
-      <c r="B83" s="50" t="s">
+      <c r="B84" s="112"/>
+      <c r="C84" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="C83" s="50" t="s">
+      <c r="D84" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="D83" s="103"/>
-      <c r="E83" s="50" t="s">
+      <c r="E84" s="103"/>
+      <c r="F84" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="F83" s="50" t="s">
+      <c r="G84" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="G83" s="103"/>
-      <c r="H83" s="51" t="s">
+      <c r="H84" s="103"/>
+      <c r="I84" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="I83" s="51" t="s">
+      <c r="J84" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="J83" s="50" t="s">
+      <c r="K84" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="K83" s="103"/>
-      <c r="L83" s="50"/>
-      <c r="M83" s="50"/>
-      <c r="N83" s="103"/>
-      <c r="O83" s="51" t="s">
+      <c r="L84" s="103"/>
+      <c r="M84" s="50"/>
+      <c r="N84" s="50"/>
+      <c r="O84" s="103"/>
+      <c r="P84" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="P83" s="103"/>
-      <c r="Q83" s="51" t="s">
+      <c r="Q84" s="103"/>
+      <c r="R84" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="R83" s="51" t="s">
+      <c r="S84" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="S83" s="103"/>
-      <c r="T83" s="103"/>
-      <c r="U83" s="50"/>
-      <c r="V83" s="103"/>
-      <c r="W83" s="51" t="s">
+      <c r="T84" s="103"/>
+      <c r="U84" s="103"/>
+      <c r="V84" s="50"/>
+      <c r="W84" s="103"/>
+      <c r="X84" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="X83" s="103"/>
-      <c r="Y83" s="51"/>
-      <c r="Z83" s="52" t="s">
+      <c r="Y84" s="103"/>
+      <c r="Z84" s="51"/>
+      <c r="AA84" s="52" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A84" s="138"/>
-      <c r="B84" s="12" t="s">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A85" s="129"/>
+      <c r="B85" s="113"/>
+      <c r="C85" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="D85" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D84" s="103"/>
-      <c r="E84" s="12" t="s">
+      <c r="E85" s="103"/>
+      <c r="F85" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="F84" s="12" t="s">
+      <c r="G85" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="G84" s="103"/>
-      <c r="H84" s="32" t="s">
+      <c r="H85" s="103"/>
+      <c r="I85" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="I84" s="32" t="s">
+      <c r="J85" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="J84" s="12" t="s">
+      <c r="K85" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="K84" s="103"/>
-      <c r="L84" s="12"/>
-      <c r="M84" s="12"/>
-      <c r="N84" s="103"/>
-      <c r="O84" s="32" t="s">
+      <c r="L85" s="103"/>
+      <c r="M85" s="12"/>
+      <c r="N85" s="12"/>
+      <c r="O85" s="103"/>
+      <c r="P85" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="P84" s="103"/>
-      <c r="Q84" s="32" t="s">
+      <c r="Q85" s="103"/>
+      <c r="R85" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="R84" s="32" t="s">
+      <c r="S85" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="S84" s="103"/>
-      <c r="T84" s="103"/>
-      <c r="U84" s="12"/>
-      <c r="V84" s="103"/>
-      <c r="W84" s="32" t="s">
+      <c r="T85" s="103"/>
+      <c r="U85" s="103"/>
+      <c r="V85" s="12"/>
+      <c r="W85" s="103"/>
+      <c r="X85" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="X84" s="103"/>
-      <c r="Y84" s="32"/>
-      <c r="Z84" s="12"/>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A85" s="138"/>
-      <c r="B85" s="12" t="s">
+      <c r="Y85" s="103"/>
+      <c r="Z85" s="32"/>
+      <c r="AA85" s="12"/>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A86" s="129"/>
+      <c r="B86" s="113"/>
+      <c r="C86" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="D86" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D85" s="97"/>
-      <c r="E85" s="12" t="s">
+      <c r="E86" s="97"/>
+      <c r="F86" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="F85" s="12" t="s">
+      <c r="G86" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="G85" s="97"/>
-      <c r="H85" s="31" t="s">
+      <c r="H86" s="97"/>
+      <c r="I86" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="I85" s="31" t="s">
+      <c r="J86" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="J85" s="12" t="s">
+      <c r="K86" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="K85" s="97"/>
-      <c r="L85" s="12"/>
-      <c r="M85" s="12"/>
-      <c r="N85" s="97"/>
-      <c r="O85" s="31" t="s">
+      <c r="L86" s="97"/>
+      <c r="M86" s="12"/>
+      <c r="N86" s="12"/>
+      <c r="O86" s="97"/>
+      <c r="P86" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="P85" s="97"/>
-      <c r="Q85" s="31" t="s">
+      <c r="Q86" s="97"/>
+      <c r="R86" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="R85" s="31" t="s">
+      <c r="S86" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="S85" s="97"/>
-      <c r="T85" s="97"/>
-      <c r="U85" s="12"/>
-      <c r="V85" s="97"/>
-      <c r="W85" s="31" t="s">
+      <c r="T86" s="97"/>
+      <c r="U86" s="97"/>
+      <c r="V86" s="12"/>
+      <c r="W86" s="97"/>
+      <c r="X86" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="X85" s="97"/>
-      <c r="Y85" s="31"/>
-      <c r="Z85" s="12"/>
-    </row>
-    <row r="86" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A86" s="139"/>
-      <c r="B86" s="38" t="s">
+      <c r="Y86" s="97"/>
+      <c r="Z86" s="31"/>
+      <c r="AA86" s="12"/>
+    </row>
+    <row r="87" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="130"/>
+      <c r="B87" s="114"/>
+      <c r="C87" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="C86" s="38" t="s">
+      <c r="D87" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="D86" s="97"/>
-      <c r="E86" s="38" t="s">
+      <c r="E87" s="97"/>
+      <c r="F87" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="F86" s="38" t="s">
+      <c r="G87" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="G86" s="97"/>
-      <c r="H86" s="39" t="s">
+      <c r="H87" s="97"/>
+      <c r="I87" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="I86" s="39" t="s">
+      <c r="J87" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="J86" s="38" t="s">
+      <c r="K87" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="K86" s="97"/>
-      <c r="L86" s="38"/>
-      <c r="M86" s="38"/>
-      <c r="N86" s="97"/>
-      <c r="O86" s="39" t="s">
+      <c r="L87" s="97"/>
+      <c r="M87" s="38"/>
+      <c r="N87" s="38"/>
+      <c r="O87" s="97"/>
+      <c r="P87" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="P86" s="97"/>
-      <c r="Q86" s="39" t="s">
+      <c r="Q87" s="97"/>
+      <c r="R87" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="R86" s="39" t="s">
+      <c r="S87" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="S86" s="97"/>
-      <c r="T86" s="97"/>
-      <c r="U86" s="38"/>
-      <c r="V86" s="97"/>
-      <c r="W86" s="39" t="s">
+      <c r="T87" s="97"/>
+      <c r="U87" s="97"/>
+      <c r="V87" s="38"/>
+      <c r="W87" s="97"/>
+      <c r="X87" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="X86" s="97"/>
-      <c r="Y86" s="39"/>
-      <c r="Z86" s="40"/>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A87" s="128" t="s">
+      <c r="Y87" s="97"/>
+      <c r="Z87" s="39"/>
+      <c r="AA87" s="40"/>
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="A88" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="B87" s="41"/>
-      <c r="C87" s="41"/>
-      <c r="D87" s="104"/>
-      <c r="E87" s="41"/>
-      <c r="F87" s="41"/>
-      <c r="G87" s="104"/>
-      <c r="H87" s="42"/>
-      <c r="I87" s="42"/>
-      <c r="J87" s="41"/>
-      <c r="K87" s="104"/>
-      <c r="L87" s="41"/>
-      <c r="M87" s="41"/>
-      <c r="N87" s="104"/>
-      <c r="O87" s="43" t="s">
+      <c r="B88" s="165"/>
+      <c r="C88" s="41"/>
+      <c r="D88" s="41"/>
+      <c r="E88" s="104"/>
+      <c r="F88" s="41"/>
+      <c r="G88" s="41"/>
+      <c r="H88" s="104"/>
+      <c r="I88" s="42"/>
+      <c r="J88" s="42"/>
+      <c r="K88" s="41"/>
+      <c r="L88" s="104"/>
+      <c r="M88" s="41"/>
+      <c r="N88" s="41"/>
+      <c r="O88" s="104"/>
+      <c r="P88" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="P87" s="104"/>
-      <c r="Q87" s="43" t="s">
+      <c r="Q88" s="104"/>
+      <c r="R88" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="R87" s="43" t="s">
+      <c r="S88" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="S87" s="104"/>
-      <c r="T87" s="104"/>
-      <c r="U87" s="41"/>
-      <c r="V87" s="104"/>
-      <c r="W87" s="89" t="s">
+      <c r="T88" s="104"/>
+      <c r="U88" s="104"/>
+      <c r="V88" s="41"/>
+      <c r="W88" s="104"/>
+      <c r="X88" s="89" t="s">
         <v>175</v>
       </c>
-      <c r="X87" s="104"/>
-      <c r="Y87" s="43"/>
-      <c r="Z87" s="44"/>
-    </row>
-    <row r="88" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="129"/>
-      <c r="B88" s="37"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="99"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="99"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
-      <c r="J88" s="37"/>
-      <c r="K88" s="99"/>
-      <c r="L88" s="37"/>
-      <c r="M88" s="37"/>
-      <c r="N88" s="99"/>
-      <c r="O88" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="P88" s="99"/>
-      <c r="Q88" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="R88" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="S88" s="99"/>
-      <c r="T88" s="99"/>
-      <c r="U88" s="37"/>
-      <c r="V88" s="99"/>
-      <c r="W88" s="90" t="s">
-        <v>176</v>
-      </c>
-      <c r="X88" s="99"/>
-      <c r="Y88" s="29"/>
-      <c r="Z88" s="45" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="89" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A89" s="129"/>
-      <c r="B89" s="37"/>
+      <c r="Y88" s="104"/>
+      <c r="Z88" s="43"/>
+      <c r="AA88" s="44"/>
+    </row>
+    <row r="89" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="146"/>
+      <c r="B89" s="166"/>
       <c r="C89" s="37"/>
-      <c r="D89" s="99"/>
-      <c r="E89" s="37"/>
+      <c r="D89" s="37"/>
+      <c r="E89" s="99"/>
       <c r="F89" s="37"/>
-      <c r="G89" s="99"/>
-      <c r="H89" s="37"/>
+      <c r="G89" s="37"/>
+      <c r="H89" s="99"/>
       <c r="I89" s="37"/>
       <c r="J89" s="37"/>
-      <c r="K89" s="99"/>
-      <c r="L89" s="37"/>
+      <c r="K89" s="37"/>
+      <c r="L89" s="99"/>
       <c r="M89" s="37"/>
-      <c r="N89" s="99"/>
-      <c r="O89" s="29" t="s">
+      <c r="N89" s="37"/>
+      <c r="O89" s="99"/>
+      <c r="P89" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q89" s="99"/>
+      <c r="R89" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="S89" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="T89" s="99"/>
+      <c r="U89" s="99"/>
+      <c r="V89" s="37"/>
+      <c r="W89" s="99"/>
+      <c r="X89" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y89" s="99"/>
+      <c r="Z89" s="29"/>
+      <c r="AA89" s="45" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="146"/>
+      <c r="B90" s="166"/>
+      <c r="C90" s="37"/>
+      <c r="D90" s="37"/>
+      <c r="E90" s="99"/>
+      <c r="F90" s="37"/>
+      <c r="G90" s="37"/>
+      <c r="H90" s="99"/>
+      <c r="I90" s="37"/>
+      <c r="J90" s="37"/>
+      <c r="K90" s="37"/>
+      <c r="L90" s="99"/>
+      <c r="M90" s="37"/>
+      <c r="N90" s="37"/>
+      <c r="O90" s="99"/>
+      <c r="P90" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="P89" s="99"/>
-      <c r="Q89" s="29" t="s">
+      <c r="Q90" s="99"/>
+      <c r="R90" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="R89" s="29" t="s">
+      <c r="S90" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="S89" s="99"/>
-      <c r="T89" s="99"/>
-      <c r="U89" s="37"/>
-      <c r="V89" s="99"/>
-      <c r="W89" s="91" t="s">
+      <c r="T90" s="99"/>
+      <c r="U90" s="99"/>
+      <c r="V90" s="37"/>
+      <c r="W90" s="99"/>
+      <c r="X90" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="X89" s="99"/>
-      <c r="Y89" s="29"/>
-      <c r="Z89" s="45" t="s">
+      <c r="Y90" s="99"/>
+      <c r="Z90" s="29"/>
+      <c r="AA90" s="45" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="90" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A90" s="130"/>
-      <c r="B90" s="46"/>
-      <c r="C90" s="46"/>
-      <c r="D90" s="104"/>
-      <c r="E90" s="46"/>
-      <c r="F90" s="46"/>
-      <c r="G90" s="104"/>
-      <c r="H90" s="46"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="46"/>
-      <c r="K90" s="104"/>
-      <c r="L90" s="46"/>
-      <c r="M90" s="46"/>
-      <c r="N90" s="104"/>
-      <c r="O90" s="47" t="s">
+    <row r="91" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="147"/>
+      <c r="B91" s="167"/>
+      <c r="C91" s="46"/>
+      <c r="D91" s="46"/>
+      <c r="E91" s="104"/>
+      <c r="F91" s="46"/>
+      <c r="G91" s="46"/>
+      <c r="H91" s="104"/>
+      <c r="I91" s="46"/>
+      <c r="J91" s="46"/>
+      <c r="K91" s="46"/>
+      <c r="L91" s="104"/>
+      <c r="M91" s="46"/>
+      <c r="N91" s="46"/>
+      <c r="O91" s="104"/>
+      <c r="P91" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="P90" s="104"/>
-      <c r="Q90" s="47" t="s">
+      <c r="Q91" s="104"/>
+      <c r="R91" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="R90" s="47" t="s">
+      <c r="S91" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="S90" s="104"/>
-      <c r="T90" s="104"/>
-      <c r="U90" s="46"/>
-      <c r="V90" s="104"/>
-      <c r="W90" s="92" t="s">
+      <c r="T91" s="104"/>
+      <c r="U91" s="104"/>
+      <c r="V91" s="46"/>
+      <c r="W91" s="104"/>
+      <c r="X91" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="X90" s="104"/>
-      <c r="Y90" s="47"/>
-      <c r="Z90" s="48"/>
-    </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="Y94" s="28"/>
+      <c r="Y91" s="104"/>
+      <c r="Z91" s="47"/>
+      <c r="AA91" s="48"/>
+    </row>
+    <row r="95" spans="1:27" x14ac:dyDescent="0.4">
+      <c r="Z95" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="139">
-    <mergeCell ref="A28:A39"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="A76:A78"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="A61:A71"/>
-    <mergeCell ref="I61:I63"/>
-    <mergeCell ref="I64:I66"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="H67:H69"/>
-    <mergeCell ref="H64:H66"/>
-    <mergeCell ref="H61:H63"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="J46:J47"/>
-    <mergeCell ref="J48:J49"/>
-    <mergeCell ref="J52:J53"/>
-    <mergeCell ref="Q61:Q63"/>
-    <mergeCell ref="Q64:Q66"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="I48:I49"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="Q67:Q69"/>
-    <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="A87:A90"/>
-    <mergeCell ref="I67:I69"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="O44:O45"/>
-    <mergeCell ref="O46:O47"/>
-    <mergeCell ref="O48:O49"/>
-    <mergeCell ref="O55:O56"/>
-    <mergeCell ref="O57:O58"/>
-    <mergeCell ref="O52:O53"/>
-    <mergeCell ref="O61:O63"/>
-    <mergeCell ref="O64:O66"/>
-    <mergeCell ref="O67:O69"/>
-    <mergeCell ref="O70:O71"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A26"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="Q34:Q35"/>
-    <mergeCell ref="Q44:Q45"/>
-    <mergeCell ref="Q46:Q47"/>
-    <mergeCell ref="Q48:Q49"/>
-    <mergeCell ref="Q52:Q53"/>
-    <mergeCell ref="Q55:Q56"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="O34:O35"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="A43:A49"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="R67:R69"/>
-    <mergeCell ref="R70:R71"/>
-    <mergeCell ref="Y34:Y35"/>
-    <mergeCell ref="Y44:Y45"/>
-    <mergeCell ref="Y46:Y47"/>
-    <mergeCell ref="Y48:Y49"/>
-    <mergeCell ref="Y52:Y53"/>
-    <mergeCell ref="Y55:Y56"/>
-    <mergeCell ref="Y57:Y58"/>
-    <mergeCell ref="Y61:Y63"/>
-    <mergeCell ref="Y64:Y66"/>
-    <mergeCell ref="Y67:Y69"/>
-    <mergeCell ref="Y70:Y71"/>
-    <mergeCell ref="W48:W49"/>
-    <mergeCell ref="R52:R53"/>
-    <mergeCell ref="R55:R56"/>
-    <mergeCell ref="R57:R58"/>
-    <mergeCell ref="R61:R63"/>
-    <mergeCell ref="R64:R66"/>
-    <mergeCell ref="R34:R35"/>
-    <mergeCell ref="R44:R45"/>
-    <mergeCell ref="R46:R47"/>
-    <mergeCell ref="R48:R49"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="J57:J58"/>
-    <mergeCell ref="Y17:Y26"/>
-    <mergeCell ref="W46:W47"/>
-    <mergeCell ref="W44:W45"/>
-    <mergeCell ref="W52:W53"/>
-    <mergeCell ref="W55:W56"/>
-    <mergeCell ref="W57:W58"/>
-    <mergeCell ref="W50:W51"/>
-    <mergeCell ref="W18:W19"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="Q57:Q58"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="M34:M35"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="U34:U35"/>
-    <mergeCell ref="U18:U19"/>
-    <mergeCell ref="T34:T35"/>
-    <mergeCell ref="T18:T19"/>
+  <mergeCells count="145">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="V35:V36"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="U35:U36"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="Z18:Z27"/>
+    <mergeCell ref="X47:X48"/>
+    <mergeCell ref="X45:X46"/>
+    <mergeCell ref="X53:X54"/>
+    <mergeCell ref="X56:X57"/>
+    <mergeCell ref="X58:X59"/>
+    <mergeCell ref="X51:X52"/>
+    <mergeCell ref="X19:X20"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="S68:S70"/>
+    <mergeCell ref="S71:S72"/>
+    <mergeCell ref="Z35:Z36"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="Z47:Z48"/>
+    <mergeCell ref="Z49:Z50"/>
+    <mergeCell ref="Z53:Z54"/>
+    <mergeCell ref="Z56:Z57"/>
+    <mergeCell ref="Z58:Z59"/>
+    <mergeCell ref="Z62:Z64"/>
+    <mergeCell ref="Z65:Z67"/>
+    <mergeCell ref="Z68:Z70"/>
+    <mergeCell ref="Z71:Z72"/>
+    <mergeCell ref="X49:X50"/>
+    <mergeCell ref="S53:S54"/>
+    <mergeCell ref="S56:S57"/>
+    <mergeCell ref="S58:S59"/>
+    <mergeCell ref="S62:S64"/>
+    <mergeCell ref="S65:S67"/>
+    <mergeCell ref="S35:S36"/>
+    <mergeCell ref="S45:S46"/>
+    <mergeCell ref="S47:S48"/>
+    <mergeCell ref="S49:S50"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A27"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="R45:R46"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="R49:R50"/>
+    <mergeCell ref="R53:R54"/>
+    <mergeCell ref="R56:R57"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="A44:A50"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="R68:R70"/>
+    <mergeCell ref="R71:R72"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="J68:J70"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="P49:P50"/>
+    <mergeCell ref="P56:P57"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="P62:P64"/>
+    <mergeCell ref="P65:P67"/>
+    <mergeCell ref="P68:P70"/>
+    <mergeCell ref="P71:P72"/>
+    <mergeCell ref="J53:J54"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="R58:R59"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="K53:K54"/>
+    <mergeCell ref="R62:R64"/>
+    <mergeCell ref="R65:R67"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J62:J64"/>
+    <mergeCell ref="J65:J67"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I68:I70"/>
+    <mergeCell ref="I65:I67"/>
+    <mergeCell ref="I62:I64"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="A29:A40"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A73:A76"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="A62:A72"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9190,7 +9561,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="146" t="s">
+      <c r="A38" s="157" t="s">
         <v>297</v>
       </c>
       <c r="B38" t="s">
@@ -9216,7 +9587,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="146"/>
+      <c r="A39" s="157"/>
       <c r="B39" t="s">
         <v>292</v>
       </c>
@@ -9240,7 +9611,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="146"/>
+      <c r="A40" s="157"/>
       <c r="C40" s="93">
         <v>38</v>
       </c>
@@ -9261,7 +9632,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="146"/>
+      <c r="A41" s="157"/>
       <c r="B41" t="s">
         <v>293</v>
       </c>
@@ -9270,7 +9641,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="146"/>
+      <c r="A42" s="157"/>
       <c r="B42" t="s">
         <v>294</v>
       </c>
@@ -9279,7 +9650,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="146"/>
+      <c r="A43" s="157"/>
       <c r="B43" t="s">
         <v>295</v>
       </c>
@@ -9288,7 +9659,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="146"/>
+      <c r="A44" s="157"/>
       <c r="B44" t="s">
         <v>296</v>
       </c>
@@ -9307,6 +9678,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100431B1C8C9D9DBE4AA0E80FF5D0349E59" ma:contentTypeVersion="5" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f7ed8c6386409f34b595d96d3c2cb336">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f8eebbbb-06cf-461a-bdd4-fdce0afb9207" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f8b92ee3a140b325dd50340e431628f3" ns3:_="">
     <xsd:import namespace="f8eebbbb-06cf-461a-bdd4-fdce0afb9207"/>
@@ -9456,22 +9842,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFFF1BA6-01AE-4C7B-81CA-4E0B23197A87}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f8eebbbb-06cf-461a-bdd4-fdce0afb9207"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0288E754-9E21-4B46-B6F4-7FC0FB88B792}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63B34AA1-4D99-4870-B3C7-12AFF67D4A6A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9487,28 +9882,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0288E754-9E21-4B46-B6F4-7FC0FB88B792}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFFF1BA6-01AE-4C7B-81CA-4E0B23197A87}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f8eebbbb-06cf-461a-bdd4-fdce0afb9207"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>